--- a/entrega_1/docs/cronograma.xlsx
+++ b/entrega_1/docs/cronograma.xlsx
@@ -35,7 +35,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Supuesto: lunes 28/09/2026. Ajústelo al calendario real del curso; todas las fechas del cronograma se recalculan desde esta celda.</t>
+          <t xml:space="preserve">Inicio del proyecto: lunes 28/09/2026. Las actividades se calculan desde esta fecha.</t>
         </r>
       </text>
     </comment>
@@ -47,7 +47,19 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Por defecto es la fecha de hoy (=TODAY()). Escriba una fecha fija si quiere congelar el estado de las tareas a un corte específico.</t>
+          <t xml:space="preserve">Por defecto es la fecha de hoy (=TODAY()). Escriba una fecha fija si quiere congelar el estado a un corte.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Fechas oficiales del curso confirmadas por el equipo el 09/10/2026.</t>
         </r>
       </text>
     </comment>
@@ -102,7 +114,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="157">
   <si>
     <t xml:space="preserve">Cronograma del proyecto — Identificación de especies por su canto (Grupo 4)</t>
   </si>
@@ -122,6 +134,18 @@
     <t xml:space="preserve">Semana actual del proyecto</t>
   </si>
   <si>
+    <t xml:space="preserve">Fechas oficiales de entrega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega 1 (20 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega 2 (10 %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega 3 (70 %)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Equipo (lista para la columna Responsable)</t>
   </si>
   <si>
@@ -146,25 +170,25 @@
     <t xml:space="preserve">Cómo usar este archivo</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Celdas con fondo amarillo y texto azul = datos de entrada: fecha de inicio, desfase, duración, responsable y % de avance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Las demás celdas se calculan con fórmulas: fechas, semana, estado, resumen por etapa y diagrama de Gantt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Desfase = días desde la fecha de inicio hasta que empieza la actividad. Duración = días calendario (0 = hito).</t>
+    <t xml:space="preserve">1. Celdas con fondo amarillo y texto azul = datos de entrada: fechas de inicio y de entrega, desfase, duración, responsable y % de avance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Las demás celdas se calculan con fórmulas: fechas, semana, estado, holgura, resumen por etapa y diagrama de Gantt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Desfase = días desde la fecha de inicio hasta que empieza la actividad. Duración = días calendario. Los hitos toman la fecha oficial de esta hoja.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Estado: Completada (100 %), Pendiente (aún no inicia), En curso o Atrasada (pasó la fecha fin sin llegar al 100 %).</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Actualice el % de avance cada semana. Las fechas son tentativas hasta confirmar el calendario del curso.</t>
+    <t xml:space="preserve">5. En la hoja Resumen, la holgura debe ser de al menos 1 día: si es menor, la última actividad de la etapa termina tarde frente a la entrega.</t>
   </si>
   <si>
     <t xml:space="preserve">Plan de actividades y cronograma — Proyecto 1 · Innovación Tecnológica con IA · Grupo 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Fechas calculadas desde la hoja Parámetros. Celdas amarillas = datos editables.</t>
+    <t xml:space="preserve">Fechas calculadas desde la hoja Parámetros (inicio y fechas oficiales de entrega). Celdas amarillas = datos editables.</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de corte:</t>
@@ -278,15 +302,33 @@
     <t xml:space="preserve">1.8</t>
   </si>
   <si>
-    <t xml:space="preserve">Redacción y revisión del reporte 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">docs/reporte_entrega_1.md</t>
+    <t xml:space="preserve">Redacción del reporte 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Borrador de docs/reporte_entrega_1.md</t>
   </si>
   <si>
     <t xml:space="preserve">1.3, 1.5, 1.6</t>
   </si>
   <si>
+    <t xml:space="preserve">1.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión del reporte por el equipo y ajustes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comentarios incorporados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versión final y publicación de la Entrega 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rama main actualizada</t>
+  </si>
+  <si>
     <t xml:space="preserve">H1</t>
   </si>
   <si>
@@ -299,16 +341,16 @@
     <t xml:space="preserve">2.1</t>
   </si>
   <si>
-    <t xml:space="preserve">Selección de especies objetivo y criterios de inclusión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista de especies</t>
+    <t xml:space="preserve">Clave de API, metadatos de la región y selección de especies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista de especies objetivo</t>
   </si>
   <si>
     <t xml:space="preserve">2.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Clave de API y descarga de grabaciones y metadatos</t>
+    <t xml:space="preserve">Descarga de grabaciones y metadatos</t>
   </si>
   <si>
     <t xml:space="preserve">data/raw y metadatos</t>
@@ -371,6 +413,15 @@
     <t xml:space="preserve">2.6, 2.7</t>
   </si>
   <si>
+    <t xml:space="preserve">2.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión y publicación de la Entrega 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carpeta entrega_2 en main</t>
+  </si>
+  <si>
     <t xml:space="preserve">H2</t>
   </si>
   <si>
@@ -389,7 +440,7 @@
     <t xml:space="preserve">3.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Embeddings bioacústicos (BirdNET o Perch) + clasificador</t>
+    <t xml:space="preserve">Embeddings bioacústicos (BirdNET o Perch 2.0) + clasificador</t>
   </si>
   <si>
     <t xml:space="preserve">3.3</t>
@@ -479,7 +530,7 @@
     <t xml:space="preserve">◆</t>
   </si>
   <si>
-    <t xml:space="preserve">Hito de entrega · columna gris = semana de la fecha de corte</t>
+    <t xml:space="preserve">Entrega oficial · columna gris = semana de la fecha de corte</t>
   </si>
   <si>
     <t xml:space="preserve">Resumen por etapa (calculado desde la hoja Cronograma)</t>
@@ -507,6 +558,9 @@
   </si>
   <si>
     <t xml:space="preserve">Días para la entrega</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holgura antes de la entrega (días)</t>
   </si>
   <si>
     <t xml:space="preserve">Total del proyecto</t>
@@ -537,13 +591,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0"/>
     <numFmt numFmtId="167" formatCode="dd/mm"/>
     <numFmt numFmtId="168" formatCode="\S0"/>
-    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="169" formatCode="@"/>
+    <numFmt numFmtId="170" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="General"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -750,7 +806,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="36">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -807,6 +863,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -823,7 +883,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -831,12 +891,16 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -855,15 +919,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -871,7 +939,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1184,7 +1260,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
@@ -1218,8 +1294,8 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="n">
-        <f aca="false">MAX(Cronograma!$I$6:$I$33)</f>
-        <v>46369</v>
+        <f aca="false">MAX(Cronograma!$I$6:$I$36)</f>
+        <v>46357</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1228,7 +1304,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">B5-B3+1</f>
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1249,60 +1325,89 @@
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="B10" s="3" t="n">
+        <v>46314</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
+      <c r="B11" s="3" t="n">
+        <v>46345</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="B12" s="3" t="n">
+        <v>46357</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>13</v>
+      <c r="A18" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1322,12 +1427,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
@@ -1336,22 +1441,22 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="14" style="0" width="6.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="14" style="0" width="6.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="L3" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M3" s="10" t="n">
         <f aca="false">Parámetros!$B$4</f>
@@ -1403,50 +1508,46 @@
         <f aca="false">Parámetros!$B$3+7*(X$5-1)</f>
         <v>46363</v>
       </c>
-      <c r="Y4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(Y$5-1)</f>
-        <v>46370</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="L5" s="12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M5" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="N5" s="13" t="n">
         <v>1</v>
@@ -1481,2647 +1582,2802 @@
       <c r="X5" s="13" t="n">
         <v>11</v>
       </c>
-      <c r="Y5" s="13" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="14" t="n">
+        <v>39</v>
+      </c>
+      <c r="B6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="16" t="n">
+      <c r="C6" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="16" t="n">
+      <c r="G6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H6" s="17" t="n">
+      <c r="H6" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F6</f>
         <v>46293</v>
       </c>
-      <c r="I6" s="17" t="n">
+      <c r="I6" s="18" t="n">
         <f aca="false">IF(G6=0,H6,H6+G6-1)</f>
         <v>46295</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="15" t="n">
         <f aca="false">INT((H6-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="18" t="n">
+      <c r="K6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="L6" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="14" t="str">
+      <c r="M6" s="15" t="str">
         <f aca="false">IF(L6&gt;=1,"Completada",IF($M$3&lt;H6,"Pendiente",IF($M$3&gt;I6,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N6" s="19" t="str">
+      <c r="N6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=N$4,$H6&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O6" s="19" t="str">
+      <c r="O6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=O$4,$H6&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P6" s="19" t="str">
+      <c r="P6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=P$4,$H6&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q6" s="19" t="str">
+      <c r="Q6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=Q$4,$H6&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R6" s="19" t="str">
+      <c r="R6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=R$4,$H6&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S6" s="19" t="str">
+      <c r="S6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=S$4,$H6&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T6" s="19" t="str">
+      <c r="T6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=T$4,$H6&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U6" s="19" t="str">
+      <c r="U6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=U$4,$H6&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V6" s="19" t="str">
+      <c r="V6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=V$4,$H6&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W6" s="19" t="str">
+      <c r="W6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=W$4,$H6&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X6" s="19" t="str">
+      <c r="X6" s="20" t="str">
         <f aca="false">IF(AND($G6=0,$H6&gt;=X$4,$H6&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y6" s="19" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=Y$4,$H6&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="14" t="n">
+        <v>43</v>
+      </c>
+      <c r="B7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="16" t="n">
+      <c r="C7" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="H7" s="17" t="n">
+      <c r="H7" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F7</f>
         <v>46295</v>
       </c>
-      <c r="I7" s="17" t="n">
+      <c r="I7" s="18" t="n">
         <f aca="false">IF(G7=0,H7,H7+G7-1)</f>
         <v>46300</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="15" t="n">
         <f aca="false">INT((H7-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
-      <c r="K7" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="18" t="n">
+      <c r="K7" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="14" t="str">
+      <c r="M7" s="15" t="str">
         <f aca="false">IF(L7&gt;=1,"Completada",IF($M$3&lt;H7,"Pendiente",IF($M$3&gt;I7,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N7" s="19" t="str">
+      <c r="N7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=N$4,$H7&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O7" s="19" t="str">
+      <c r="O7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=O$4,$H7&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P7" s="19" t="str">
+      <c r="P7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=P$4,$H7&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q7" s="19" t="str">
+      <c r="Q7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=Q$4,$H7&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R7" s="19" t="str">
+      <c r="R7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=R$4,$H7&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S7" s="19" t="str">
+      <c r="S7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=S$4,$H7&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T7" s="19" t="str">
+      <c r="T7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=T$4,$H7&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U7" s="19" t="str">
+      <c r="U7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=U$4,$H7&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V7" s="19" t="str">
+      <c r="V7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=V$4,$H7&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W7" s="19" t="str">
+      <c r="W7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=W$4,$H7&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X7" s="19" t="str">
+      <c r="X7" s="20" t="str">
         <f aca="false">IF(AND($G7=0,$H7&gt;=X$4,$H7&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y7" s="19" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=Y$4,$H7&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="14" t="n">
+        <v>46</v>
+      </c>
+      <c r="B8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="16" t="n">
+      <c r="C8" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="16" t="n">
+      <c r="G8" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="17" t="n">
+      <c r="H8" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F8</f>
         <v>46298</v>
       </c>
-      <c r="I8" s="17" t="n">
+      <c r="I8" s="18" t="n">
         <f aca="false">IF(G8=0,H8,H8+G8-1)</f>
         <v>46301</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="15" t="n">
         <f aca="false">INT((H8-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
-      <c r="K8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="18" t="n">
+      <c r="K8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="14" t="str">
+      <c r="M8" s="15" t="str">
         <f aca="false">IF(L8&gt;=1,"Completada",IF($M$3&lt;H8,"Pendiente",IF($M$3&gt;I8,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N8" s="19" t="str">
+      <c r="N8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=N$4,$H8&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O8" s="19" t="str">
+      <c r="O8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=O$4,$H8&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P8" s="19" t="str">
+      <c r="P8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=P$4,$H8&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q8" s="19" t="str">
+      <c r="Q8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=Q$4,$H8&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R8" s="19" t="str">
+      <c r="R8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=R$4,$H8&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S8" s="19" t="str">
+      <c r="S8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=S$4,$H8&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T8" s="19" t="str">
+      <c r="T8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=T$4,$H8&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U8" s="19" t="str">
+      <c r="U8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=U$4,$H8&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V8" s="19" t="str">
+      <c r="V8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=V$4,$H8&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W8" s="19" t="str">
+      <c r="W8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=W$4,$H8&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X8" s="19" t="str">
+      <c r="X8" s="20" t="str">
         <f aca="false">IF(AND($G8=0,$H8&gt;=X$4,$H8&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y8" s="19" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=Y$4,$H8&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="14" t="n">
+        <v>49</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="16" t="n">
+      <c r="C9" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="16" t="n">
+      <c r="G9" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H9" s="17" t="n">
+      <c r="H9" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F9</f>
         <v>46295</v>
       </c>
-      <c r="I9" s="17" t="n">
+      <c r="I9" s="18" t="n">
         <f aca="false">IF(G9=0,H9,H9+G9-1)</f>
         <v>46303</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="15" t="n">
         <f aca="false">INT((H9-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="18" t="n">
+      <c r="K9" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="14" t="str">
+      <c r="M9" s="15" t="str">
         <f aca="false">IF(L9&gt;=1,"Completada",IF($M$3&lt;H9,"Pendiente",IF($M$3&gt;I9,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N9" s="19" t="str">
+      <c r="N9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=N$4,$H9&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O9" s="19" t="str">
+      <c r="O9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=O$4,$H9&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P9" s="19" t="str">
+      <c r="P9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=P$4,$H9&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q9" s="19" t="str">
+      <c r="Q9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=Q$4,$H9&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R9" s="19" t="str">
+      <c r="R9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=R$4,$H9&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S9" s="19" t="str">
+      <c r="S9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=S$4,$H9&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T9" s="19" t="str">
+      <c r="T9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=T$4,$H9&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U9" s="19" t="str">
+      <c r="U9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=U$4,$H9&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V9" s="19" t="str">
+      <c r="V9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=V$4,$H9&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W9" s="19" t="str">
+      <c r="W9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=W$4,$H9&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X9" s="19" t="str">
+      <c r="X9" s="20" t="str">
         <f aca="false">IF(AND($G9=0,$H9&gt;=X$4,$H9&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y9" s="19" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=Y$4,$H9&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="14" t="n">
+        <v>52</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="16" t="n">
+      <c r="C10" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="16" t="n">
+      <c r="G10" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="H10" s="17" t="n">
+      <c r="H10" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F10</f>
         <v>46300</v>
       </c>
-      <c r="I10" s="17" t="n">
+      <c r="I10" s="18" t="n">
         <f aca="false">IF(G10=0,H10,H10+G10-1)</f>
         <v>46303</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="15" t="n">
         <f aca="false">INT((H10-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
-      <c r="K10" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="18" t="n">
+      <c r="K10" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M10" s="14" t="str">
+      <c r="M10" s="15" t="str">
         <f aca="false">IF(L10&gt;=1,"Completada",IF($M$3&lt;H10,"Pendiente",IF($M$3&gt;I10,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N10" s="19" t="str">
+      <c r="N10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=N$4,$H10&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O10" s="19" t="str">
+      <c r="O10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=O$4,$H10&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P10" s="19" t="str">
+      <c r="P10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=P$4,$H10&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q10" s="19" t="str">
+      <c r="Q10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=Q$4,$H10&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R10" s="19" t="str">
+      <c r="R10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=R$4,$H10&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S10" s="19" t="str">
+      <c r="S10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=S$4,$H10&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T10" s="19" t="str">
+      <c r="T10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=T$4,$H10&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U10" s="19" t="str">
+      <c r="U10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=U$4,$H10&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V10" s="19" t="str">
+      <c r="V10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=V$4,$H10&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W10" s="19" t="str">
+      <c r="W10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=W$4,$H10&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X10" s="19" t="str">
+      <c r="X10" s="20" t="str">
         <f aca="false">IF(AND($G10=0,$H10&gt;=X$4,$H10&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y10" s="19" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=Y$4,$H10&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="B11" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="16" t="n">
+      <c r="C11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="G11" s="16" t="n">
+      <c r="G11" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="17" t="n">
+      <c r="H11" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F11</f>
         <v>46301</v>
       </c>
-      <c r="I11" s="17" t="n">
+      <c r="I11" s="18" t="n">
         <f aca="false">IF(G11=0,H11,H11+G11-1)</f>
         <v>46303</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="15" t="n">
         <f aca="false">INT((H11-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
-      <c r="K11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="18" t="n">
+      <c r="K11" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L11" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M11" s="14" t="str">
+      <c r="M11" s="15" t="str">
         <f aca="false">IF(L11&gt;=1,"Completada",IF($M$3&lt;H11,"Pendiente",IF($M$3&gt;I11,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N11" s="19" t="str">
+      <c r="N11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=N$4,$H11&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O11" s="19" t="str">
+      <c r="O11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=O$4,$H11&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P11" s="19" t="str">
+      <c r="P11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=P$4,$H11&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q11" s="19" t="str">
+      <c r="Q11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=Q$4,$H11&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R11" s="19" t="str">
+      <c r="R11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=R$4,$H11&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S11" s="19" t="str">
+      <c r="S11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=S$4,$H11&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T11" s="19" t="str">
+      <c r="T11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=T$4,$H11&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U11" s="19" t="str">
+      <c r="U11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=U$4,$H11&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V11" s="19" t="str">
+      <c r="V11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=V$4,$H11&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W11" s="19" t="str">
+      <c r="W11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=W$4,$H11&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X11" s="19" t="str">
+      <c r="X11" s="20" t="str">
         <f aca="false">IF(AND($G11=0,$H11&gt;=X$4,$H11&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y11" s="19" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=Y$4,$H11&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="B12" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B12" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="16" t="n">
+      <c r="C12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="17" t="n">
+      <c r="H12" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F12</f>
         <v>46302</v>
       </c>
-      <c r="I12" s="17" t="n">
+      <c r="I12" s="18" t="n">
         <f aca="false">IF(G12=0,H12,H12+G12-1)</f>
         <v>46304</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="15" t="n">
         <f aca="false">INT((H12-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
-      <c r="K12" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="18" t="n">
+      <c r="K12" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L12" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="14" t="str">
+      <c r="M12" s="15" t="str">
         <f aca="false">IF(L12&gt;=1,"Completada",IF($M$3&lt;H12,"Pendiente",IF($M$3&gt;I12,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
-      <c r="N12" s="19" t="str">
+      <c r="N12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=N$4,$H12&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O12" s="19" t="str">
+      <c r="O12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=O$4,$H12&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P12" s="19" t="str">
+      <c r="P12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=P$4,$H12&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q12" s="19" t="str">
+      <c r="Q12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=Q$4,$H12&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R12" s="19" t="str">
+      <c r="R12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=R$4,$H12&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S12" s="19" t="str">
+      <c r="S12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=S$4,$H12&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T12" s="19" t="str">
+      <c r="T12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=T$4,$H12&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U12" s="19" t="str">
+      <c r="U12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=U$4,$H12&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V12" s="19" t="str">
+      <c r="V12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=V$4,$H12&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W12" s="19" t="str">
+      <c r="W12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=W$4,$H12&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X12" s="19" t="str">
+      <c r="X12" s="20" t="str">
         <f aca="false">IF(AND($G12=0,$H12&gt;=X$4,$H12&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y12" s="19" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=Y$4,$H12&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="B13" s="14" t="n">
+        <v>61</v>
+      </c>
+      <c r="B13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C13" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="16" t="n">
+      <c r="C13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="17" t="n">
+      <c r="G13" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F13</f>
         <v>46303</v>
       </c>
-      <c r="I13" s="17" t="n">
+      <c r="I13" s="18" t="n">
         <f aca="false">IF(G13=0,H13,H13+G13-1)</f>
-        <v>46305</v>
-      </c>
-      <c r="J13" s="14" t="n">
+        <v>46304</v>
+      </c>
+      <c r="J13" s="15" t="n">
         <f aca="false">INT((H13-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
-      <c r="K13" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" s="18" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M13" s="14" t="str">
+      <c r="K13" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15" t="str">
         <f aca="false">IF(L13&gt;=1,"Completada",IF($M$3&lt;H13,"Pendiente",IF($M$3&gt;I13,"Atrasada","En curso")))</f>
-        <v>En curso</v>
-      </c>
-      <c r="N13" s="19" t="str">
+        <v>Completada</v>
+      </c>
+      <c r="N13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=N$4,$H13&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O13" s="19" t="str">
+      <c r="O13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=O$4,$H13&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P13" s="19" t="str">
+      <c r="P13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=P$4,$H13&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q13" s="19" t="str">
+      <c r="Q13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=Q$4,$H13&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R13" s="19" t="str">
+      <c r="R13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=R$4,$H13&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S13" s="19" t="str">
+      <c r="S13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=S$4,$H13&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T13" s="19" t="str">
+      <c r="T13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=T$4,$H13&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U13" s="19" t="str">
+      <c r="U13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=U$4,$H13&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V13" s="19" t="str">
+      <c r="V13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=V$4,$H13&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W13" s="19" t="str">
+      <c r="W13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=W$4,$H13&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X13" s="19" t="str">
+      <c r="X13" s="20" t="str">
         <f aca="false">IF(AND($G13=0,$H13&gt;=X$4,$H13&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y13" s="19" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=Y$4,$H13&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B14" s="14" t="n">
+      <c r="A14" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="G14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="17" t="n">
+      <c r="C14" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F14</f>
-        <v>46306</v>
-      </c>
-      <c r="I14" s="17" t="n">
+        <v>46305</v>
+      </c>
+      <c r="I14" s="18" t="n">
         <f aca="false">IF(G14=0,H14,H14+G14-1)</f>
-        <v>46306</v>
-      </c>
-      <c r="J14" s="14" t="n">
+        <v>46310</v>
+      </c>
+      <c r="J14" s="15" t="n">
         <f aca="false">INT((H14-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
-      <c r="K14" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="L14" s="18" t="n">
+      <c r="K14" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L14" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M14" s="14" t="str">
+      <c r="M14" s="15" t="str">
         <f aca="false">IF(L14&gt;=1,"Completada",IF($M$3&lt;H14,"Pendiente",IF($M$3&gt;I14,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N14" s="19" t="str">
+      <c r="N14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=N$4,$H14&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O14" s="19" t="str">
+      <c r="O14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=O$4,$H14&lt;=O$4+6),"◆","")</f>
-        <v>◆</v>
-      </c>
-      <c r="P14" s="19" t="str">
+        <v/>
+      </c>
+      <c r="P14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=P$4,$H14&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q14" s="19" t="str">
+      <c r="Q14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=Q$4,$H14&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R14" s="19" t="str">
+      <c r="R14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=R$4,$H14&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S14" s="19" t="str">
+      <c r="S14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=S$4,$H14&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T14" s="19" t="str">
+      <c r="T14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=T$4,$H14&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U14" s="19" t="str">
+      <c r="U14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=U$4,$H14&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V14" s="19" t="str">
+      <c r="V14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=V$4,$H14&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W14" s="19" t="str">
+      <c r="W14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=W$4,$H14&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X14" s="19" t="str">
+      <c r="X14" s="20" t="str">
         <f aca="false">IF(AND($G14=0,$H14&gt;=X$4,$H14&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y14" s="19" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=Y$4,$H14&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F15</f>
-        <v>46307</v>
-      </c>
-      <c r="I15" s="17" t="n">
+        <v>46311</v>
+      </c>
+      <c r="I15" s="18" t="n">
         <f aca="false">IF(G15=0,H15,H15+G15-1)</f>
-        <v>46310</v>
-      </c>
-      <c r="J15" s="14" t="n">
+        <v>46313</v>
+      </c>
+      <c r="J15" s="15" t="n">
         <f aca="false">INT((H15-Parámetros!$B$3)/7)+1</f>
         <v>3</v>
       </c>
-      <c r="K15" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="L15" s="18" t="n">
+      <c r="K15" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L15" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M15" s="14" t="str">
+      <c r="M15" s="15" t="str">
         <f aca="false">IF(L15&gt;=1,"Completada",IF($M$3&lt;H15,"Pendiente",IF($M$3&gt;I15,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N15" s="19" t="str">
+      <c r="N15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=N$4,$H15&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O15" s="19" t="str">
+      <c r="O15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=O$4,$H15&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P15" s="19" t="str">
+      <c r="P15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=P$4,$H15&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q15" s="19" t="str">
+      <c r="Q15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=Q$4,$H15&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R15" s="19" t="str">
+      <c r="R15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=R$4,$H15&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S15" s="19" t="str">
+      <c r="S15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=S$4,$H15&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T15" s="19" t="str">
+      <c r="T15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=T$4,$H15&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U15" s="19" t="str">
+      <c r="U15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=U$4,$H15&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V15" s="19" t="str">
+      <c r="V15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=V$4,$H15&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W15" s="19" t="str">
+      <c r="W15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=W$4,$H15&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X15" s="19" t="str">
+      <c r="X15" s="20" t="str">
         <f aca="false">IF(AND($G15=0,$H15&gt;=X$4,$H15&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y15" s="19" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=Y$4,$H15&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="A16" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">H16-Parámetros!$B$3</f>
+        <v>21</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <f aca="false">Parámetros!$B$10</f>
+        <v>46314</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <f aca="false">IF(G16=0,H16,H16+G16-1)</f>
+        <v>46314</v>
+      </c>
+      <c r="J16" s="15" t="n">
+        <f aca="false">INT((H16-Parámetros!$B$3)/7)+1</f>
+        <v>4</v>
+      </c>
+      <c r="K16" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F16</f>
-        <v>46309</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <f aca="false">IF(G16=0,H16,H16+G16-1)</f>
-        <v>46315</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <f aca="false">INT((H16-Parámetros!$B$3)/7)+1</f>
-        <v>3</v>
-      </c>
-      <c r="K16" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="L16" s="18" t="n">
+      <c r="L16" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M16" s="14" t="str">
+      <c r="M16" s="15" t="str">
         <f aca="false">IF(L16&gt;=1,"Completada",IF($M$3&lt;H16,"Pendiente",IF($M$3&gt;I16,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N16" s="19" t="str">
+      <c r="N16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=N$4,$H16&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O16" s="19" t="str">
+      <c r="O16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=O$4,$H16&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P16" s="19" t="str">
+      <c r="P16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=P$4,$H16&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q16" s="19" t="str">
+      <c r="Q16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=Q$4,$H16&lt;=Q$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="R16" s="19" t="str">
+        <v>◆</v>
+      </c>
+      <c r="R16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=R$4,$H16&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S16" s="19" t="str">
+      <c r="S16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=S$4,$H16&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T16" s="19" t="str">
+      <c r="T16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=T$4,$H16&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U16" s="19" t="str">
+      <c r="U16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=U$4,$H16&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V16" s="19" t="str">
+      <c r="V16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=V$4,$H16&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W16" s="19" t="str">
+      <c r="W16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=W$4,$H16&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X16" s="19" t="str">
+      <c r="X16" s="20" t="str">
         <f aca="false">IF(AND($G16=0,$H16&gt;=X$4,$H16&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y16" s="19" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=Y$4,$H16&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B17" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C17" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H17" s="17" t="n">
+      <c r="C17" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F17</f>
-        <v>46314</v>
-      </c>
-      <c r="I17" s="17" t="n">
+        <v>46307</v>
+      </c>
+      <c r="I17" s="18" t="n">
         <f aca="false">IF(G17=0,H17,H17+G17-1)</f>
-        <v>46318</v>
-      </c>
-      <c r="J17" s="14" t="n">
+        <v>46312</v>
+      </c>
+      <c r="J17" s="15" t="n">
         <f aca="false">INT((H17-Parámetros!$B$3)/7)+1</f>
-        <v>4</v>
-      </c>
-      <c r="K17" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="L17" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="L17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M17" s="14" t="str">
+      <c r="M17" s="15" t="str">
         <f aca="false">IF(L17&gt;=1,"Completada",IF($M$3&lt;H17,"Pendiente",IF($M$3&gt;I17,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N17" s="19" t="str">
+      <c r="N17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=N$4,$H17&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O17" s="19" t="str">
+      <c r="O17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=O$4,$H17&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P17" s="19" t="str">
+      <c r="P17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=P$4,$H17&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q17" s="19" t="str">
+      <c r="Q17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=Q$4,$H17&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R17" s="19" t="str">
+      <c r="R17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=R$4,$H17&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S17" s="19" t="str">
+      <c r="S17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=S$4,$H17&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T17" s="19" t="str">
+      <c r="T17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=T$4,$H17&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U17" s="19" t="str">
+      <c r="U17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=U$4,$H17&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V17" s="19" t="str">
+      <c r="V17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=V$4,$H17&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W17" s="19" t="str">
+      <c r="W17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=W$4,$H17&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X17" s="19" t="str">
+      <c r="X17" s="20" t="str">
         <f aca="false">IF(AND($G17=0,$H17&gt;=X$4,$H17&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y17" s="19" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=Y$4,$H17&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="14" t="n">
+        <v>77</v>
+      </c>
+      <c r="B18" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H18" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F18</f>
+        <v>46311</v>
+      </c>
+      <c r="I18" s="18" t="n">
+        <f aca="false">IF(G18=0,H18,H18+G18-1)</f>
+        <v>46315</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <f aca="false">INT((H18-Parámetros!$B$3)/7)+1</f>
+        <v>3</v>
+      </c>
+      <c r="K18" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F18</f>
-        <v>46316</v>
-      </c>
-      <c r="I18" s="17" t="n">
-        <f aca="false">IF(G18=0,H18,H18+G18-1)</f>
-        <v>46322</v>
-      </c>
-      <c r="J18" s="14" t="n">
-        <f aca="false">INT((H18-Parámetros!$B$3)/7)+1</f>
-        <v>4</v>
-      </c>
-      <c r="K18" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="L18" s="18" t="n">
+      <c r="L18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M18" s="14" t="str">
+      <c r="M18" s="15" t="str">
         <f aca="false">IF(L18&gt;=1,"Completada",IF($M$3&lt;H18,"Pendiente",IF($M$3&gt;I18,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N18" s="19" t="str">
+      <c r="N18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=N$4,$H18&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O18" s="19" t="str">
+      <c r="O18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=O$4,$H18&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P18" s="19" t="str">
+      <c r="P18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=P$4,$H18&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q18" s="19" t="str">
+      <c r="Q18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=Q$4,$H18&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R18" s="19" t="str">
+      <c r="R18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=R$4,$H18&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S18" s="19" t="str">
+      <c r="S18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=S$4,$H18&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T18" s="19" t="str">
+      <c r="T18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=T$4,$H18&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U18" s="19" t="str">
+      <c r="U18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=U$4,$H18&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V18" s="19" t="str">
+      <c r="V18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=V$4,$H18&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W18" s="19" t="str">
+      <c r="W18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=W$4,$H18&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X18" s="19" t="str">
+      <c r="X18" s="20" t="str">
         <f aca="false">IF(AND($G18=0,$H18&gt;=X$4,$H18&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y18" s="19" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=Y$4,$H18&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="B19" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="B19" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C19" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="G19" s="16" t="n">
+      <c r="C19" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="G19" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F19</f>
-        <v>46319</v>
-      </c>
-      <c r="I19" s="17" t="n">
+        <v>46314</v>
+      </c>
+      <c r="I19" s="18" t="n">
         <f aca="false">IF(G19=0,H19,H19+G19-1)</f>
-        <v>46323</v>
-      </c>
-      <c r="J19" s="14" t="n">
+        <v>46318</v>
+      </c>
+      <c r="J19" s="15" t="n">
         <f aca="false">INT((H19-Parámetros!$B$3)/7)+1</f>
         <v>4</v>
       </c>
-      <c r="K19" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="L19" s="18" t="n">
+      <c r="K19" s="16" t="s">
+        <v>77</v>
+      </c>
+      <c r="L19" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M19" s="14" t="str">
+      <c r="M19" s="15" t="str">
         <f aca="false">IF(L19&gt;=1,"Completada",IF($M$3&lt;H19,"Pendiente",IF($M$3&gt;I19,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N19" s="19" t="str">
+      <c r="N19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=N$4,$H19&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O19" s="19" t="str">
+      <c r="O19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=O$4,$H19&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P19" s="19" t="str">
+      <c r="P19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=P$4,$H19&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q19" s="19" t="str">
+      <c r="Q19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=Q$4,$H19&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R19" s="19" t="str">
+      <c r="R19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=R$4,$H19&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S19" s="19" t="str">
+      <c r="S19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=S$4,$H19&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T19" s="19" t="str">
+      <c r="T19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=T$4,$H19&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U19" s="19" t="str">
+      <c r="U19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=U$4,$H19&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V19" s="19" t="str">
+      <c r="V19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=V$4,$H19&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W19" s="19" t="str">
+      <c r="W19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=W$4,$H19&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X19" s="19" t="str">
+      <c r="X19" s="20" t="str">
         <f aca="false">IF(AND($G19=0,$H19&gt;=X$4,$H19&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y19" s="19" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=Y$4,$H19&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="14" t="n">
+        <v>83</v>
+      </c>
+      <c r="B20" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F20</f>
+        <v>46315</v>
+      </c>
+      <c r="I20" s="18" t="n">
+        <f aca="false">IF(G20=0,H20,H20+G20-1)</f>
+        <v>46323</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <f aca="false">INT((H20-Parámetros!$B$3)/7)+1</f>
+        <v>4</v>
+      </c>
+      <c r="K20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H20" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F20</f>
-        <v>46321</v>
-      </c>
-      <c r="I20" s="17" t="n">
-        <f aca="false">IF(G20=0,H20,H20+G20-1)</f>
-        <v>46324</v>
-      </c>
-      <c r="J20" s="14" t="n">
-        <f aca="false">INT((H20-Parámetros!$B$3)/7)+1</f>
-        <v>5</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="L20" s="18" t="n">
+      <c r="L20" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M20" s="14" t="str">
+      <c r="M20" s="15" t="str">
         <f aca="false">IF(L20&gt;=1,"Completada",IF($M$3&lt;H20,"Pendiente",IF($M$3&gt;I20,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N20" s="19" t="str">
+      <c r="N20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=N$4,$H20&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O20" s="19" t="str">
+      <c r="O20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=O$4,$H20&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P20" s="19" t="str">
+      <c r="P20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=P$4,$H20&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q20" s="19" t="str">
+      <c r="Q20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=Q$4,$H20&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R20" s="19" t="str">
+      <c r="R20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=R$4,$H20&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S20" s="19" t="str">
+      <c r="S20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=S$4,$H20&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T20" s="19" t="str">
+      <c r="T20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=T$4,$H20&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U20" s="19" t="str">
+      <c r="U20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=U$4,$H20&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V20" s="19" t="str">
+      <c r="V20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=V$4,$H20&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W20" s="19" t="str">
+      <c r="W20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=W$4,$H20&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X20" s="19" t="str">
+      <c r="X20" s="20" t="str">
         <f aca="false">IF(AND($G20=0,$H20&gt;=X$4,$H20&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y20" s="19" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=Y$4,$H20&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="B21" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="17" t="n">
+      <c r="C21" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H21" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F21</f>
-        <v>46323</v>
-      </c>
-      <c r="I21" s="17" t="n">
+        <v>46318</v>
+      </c>
+      <c r="I21" s="18" t="n">
         <f aca="false">IF(G21=0,H21,H21+G21-1)</f>
-        <v>46329</v>
-      </c>
-      <c r="J21" s="14" t="n">
+        <v>46322</v>
+      </c>
+      <c r="J21" s="15" t="n">
         <f aca="false">INT((H21-Parámetros!$B$3)/7)+1</f>
-        <v>5</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="L21" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="14" t="str">
+      <c r="M21" s="15" t="str">
         <f aca="false">IF(L21&gt;=1,"Completada",IF($M$3&lt;H21,"Pendiente",IF($M$3&gt;I21,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N21" s="19" t="str">
+      <c r="N21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=N$4,$H21&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O21" s="19" t="str">
+      <c r="O21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=O$4,$H21&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P21" s="19" t="str">
+      <c r="P21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=P$4,$H21&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q21" s="19" t="str">
+      <c r="Q21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=Q$4,$H21&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R21" s="19" t="str">
+      <c r="R21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=R$4,$H21&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S21" s="19" t="str">
+      <c r="S21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=S$4,$H21&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T21" s="19" t="str">
+      <c r="T21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=T$4,$H21&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U21" s="19" t="str">
+      <c r="U21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=U$4,$H21&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V21" s="19" t="str">
+      <c r="V21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=V$4,$H21&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W21" s="19" t="str">
+      <c r="W21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=W$4,$H21&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X21" s="19" t="str">
+      <c r="X21" s="20" t="str">
         <f aca="false">IF(AND($G21=0,$H21&gt;=X$4,$H21&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y21" s="19" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=Y$4,$H21&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="B22" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="B22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C22" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>36</v>
-      </c>
-      <c r="G22" s="16" t="n">
+      <c r="C22" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="G22" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="H22" s="17" t="n">
+      <c r="H22" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F22</f>
-        <v>46329</v>
-      </c>
-      <c r="I22" s="17" t="n">
+        <v>46321</v>
+      </c>
+      <c r="I22" s="18" t="n">
         <f aca="false">IF(G22=0,H22,H22+G22-1)</f>
-        <v>46333</v>
-      </c>
-      <c r="J22" s="14" t="n">
+        <v>46325</v>
+      </c>
+      <c r="J22" s="15" t="n">
         <f aca="false">INT((H22-Parámetros!$B$3)/7)+1</f>
-        <v>6</v>
-      </c>
-      <c r="K22" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="L22" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L22" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M22" s="14" t="str">
+      <c r="M22" s="15" t="str">
         <f aca="false">IF(L22&gt;=1,"Completada",IF($M$3&lt;H22,"Pendiente",IF($M$3&gt;I22,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N22" s="19" t="str">
+      <c r="N22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=N$4,$H22&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O22" s="19" t="str">
+      <c r="O22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=O$4,$H22&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P22" s="19" t="str">
+      <c r="P22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=P$4,$H22&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q22" s="19" t="str">
+      <c r="Q22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=Q$4,$H22&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R22" s="19" t="str">
+      <c r="R22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=R$4,$H22&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S22" s="19" t="str">
+      <c r="S22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=S$4,$H22&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T22" s="19" t="str">
+      <c r="T22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=T$4,$H22&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U22" s="19" t="str">
+      <c r="U22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=U$4,$H22&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V22" s="19" t="str">
+      <c r="V22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=V$4,$H22&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W22" s="19" t="str">
+      <c r="W22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=W$4,$H22&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X22" s="19" t="str">
+      <c r="X22" s="20" t="str">
         <f aca="false">IF(AND($G22=0,$H22&gt;=X$4,$H22&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y22" s="19" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=Y$4,$H22&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="14" t="n">
+      <c r="A23" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="G23" s="16" t="n">
+      <c r="C23" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F23</f>
+        <v>46322</v>
+      </c>
+      <c r="I23" s="18" t="n">
+        <f aca="false">IF(G23=0,H23,H23+G23-1)</f>
+        <v>46333</v>
+      </c>
+      <c r="J23" s="15" t="n">
+        <f aca="false">INT((H23-Parámetros!$B$3)/7)+1</f>
+        <v>5</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F23</f>
-        <v>46334</v>
-      </c>
-      <c r="I23" s="17" t="n">
-        <f aca="false">IF(G23=0,H23,H23+G23-1)</f>
-        <v>46334</v>
-      </c>
-      <c r="J23" s="14" t="n">
-        <f aca="false">INT((H23-Parámetros!$B$3)/7)+1</f>
-        <v>6</v>
-      </c>
-      <c r="K23" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="14" t="str">
+      <c r="M23" s="15" t="str">
         <f aca="false">IF(L23&gt;=1,"Completada",IF($M$3&lt;H23,"Pendiente",IF($M$3&gt;I23,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N23" s="19" t="str">
+      <c r="N23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=N$4,$H23&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O23" s="19" t="str">
+      <c r="O23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=O$4,$H23&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P23" s="19" t="str">
+      <c r="P23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=P$4,$H23&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q23" s="19" t="str">
+      <c r="Q23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=Q$4,$H23&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R23" s="19" t="str">
+      <c r="R23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=R$4,$H23&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S23" s="19" t="str">
+      <c r="S23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=S$4,$H23&lt;=S$4+6),"◆","")</f>
-        <v>◆</v>
-      </c>
-      <c r="T23" s="19" t="str">
+        <v/>
+      </c>
+      <c r="T23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=T$4,$H23&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U23" s="19" t="str">
+      <c r="U23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=U$4,$H23&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V23" s="19" t="str">
+      <c r="V23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=V$4,$H23&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W23" s="19" t="str">
+      <c r="W23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=W$4,$H23&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X23" s="19" t="str">
+      <c r="X23" s="20" t="str">
         <f aca="false">IF(AND($G23=0,$H23&gt;=X$4,$H23&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y23" s="19" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=Y$4,$H23&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>42</v>
-      </c>
-      <c r="G24" s="16" t="n">
+        <v>95</v>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G24" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="H24" s="17" t="n">
+      <c r="H24" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F24</f>
-        <v>46335</v>
-      </c>
-      <c r="I24" s="17" t="n">
+        <v>46334</v>
+      </c>
+      <c r="I24" s="18" t="n">
         <f aca="false">IF(G24=0,H24,H24+G24-1)</f>
-        <v>46343</v>
-      </c>
-      <c r="J24" s="14" t="n">
+        <v>46342</v>
+      </c>
+      <c r="J24" s="15" t="n">
         <f aca="false">INT((H24-Parámetros!$B$3)/7)+1</f>
-        <v>7</v>
-      </c>
-      <c r="K24" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="L24" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M24" s="14" t="str">
+      <c r="M24" s="15" t="str">
         <f aca="false">IF(L24&gt;=1,"Completada",IF($M$3&lt;H24,"Pendiente",IF($M$3&gt;I24,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N24" s="19" t="str">
+      <c r="N24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=N$4,$H24&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O24" s="19" t="str">
+      <c r="O24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=O$4,$H24&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P24" s="19" t="str">
+      <c r="P24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=P$4,$H24&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q24" s="19" t="str">
+      <c r="Q24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=Q$4,$H24&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R24" s="19" t="str">
+      <c r="R24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=R$4,$H24&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S24" s="19" t="str">
+      <c r="S24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=S$4,$H24&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T24" s="19" t="str">
+      <c r="T24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=T$4,$H24&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U24" s="19" t="str">
+      <c r="U24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=U$4,$H24&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V24" s="19" t="str">
+      <c r="V24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=V$4,$H24&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W24" s="19" t="str">
+      <c r="W24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=W$4,$H24&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X24" s="19" t="str">
+      <c r="X24" s="20" t="str">
         <f aca="false">IF(AND($G24=0,$H24&gt;=X$4,$H24&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y24" s="19" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=Y$4,$H24&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="G25" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="H25" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F25</f>
+        <v>46342</v>
+      </c>
+      <c r="I25" s="18" t="n">
+        <f aca="false">IF(G25=0,H25,H25+G25-1)</f>
+        <v>46344</v>
+      </c>
+      <c r="J25" s="15" t="n">
+        <f aca="false">INT((H25-Parámetros!$B$3)/7)+1</f>
+        <v>8</v>
+      </c>
+      <c r="K25" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>44</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F25</f>
-        <v>46337</v>
-      </c>
-      <c r="I25" s="17" t="n">
-        <f aca="false">IF(G25=0,H25,H25+G25-1)</f>
-        <v>46345</v>
-      </c>
-      <c r="J25" s="14" t="n">
-        <f aca="false">INT((H25-Parámetros!$B$3)/7)+1</f>
-        <v>7</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="L25" s="18" t="n">
+      <c r="L25" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="14" t="str">
+      <c r="M25" s="15" t="str">
         <f aca="false">IF(L25&gt;=1,"Completada",IF($M$3&lt;H25,"Pendiente",IF($M$3&gt;I25,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N25" s="19" t="str">
+      <c r="N25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=N$4,$H25&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O25" s="19" t="str">
+      <c r="O25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=O$4,$H25&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P25" s="19" t="str">
+      <c r="P25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=P$4,$H25&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q25" s="19" t="str">
+      <c r="Q25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=Q$4,$H25&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R25" s="19" t="str">
+      <c r="R25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=R$4,$H25&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S25" s="19" t="str">
+      <c r="S25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=S$4,$H25&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T25" s="19" t="str">
+      <c r="T25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=T$4,$H25&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U25" s="19" t="str">
+      <c r="U25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=U$4,$H25&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V25" s="19" t="str">
+      <c r="V25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=V$4,$H25&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W25" s="19" t="str">
+      <c r="W25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=W$4,$H25&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X25" s="19" t="str">
+      <c r="X25" s="20" t="str">
         <f aca="false">IF(AND($G25=0,$H25&gt;=X$4,$H25&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y25" s="19" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=Y$4,$H25&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="B26" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="16" t="n">
-        <v>50</v>
-      </c>
-      <c r="G26" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F26</f>
-        <v>46343</v>
-      </c>
-      <c r="I26" s="17" t="n">
+      <c r="A26" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="C26" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <f aca="false">H26-Parámetros!$B$3</f>
+        <v>52</v>
+      </c>
+      <c r="G26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23" t="n">
+        <f aca="false">Parámetros!$B$11</f>
+        <v>46345</v>
+      </c>
+      <c r="I26" s="18" t="n">
         <f aca="false">IF(G26=0,H26,H26+G26-1)</f>
-        <v>46349</v>
-      </c>
-      <c r="J26" s="14" t="n">
+        <v>46345</v>
+      </c>
+      <c r="J26" s="15" t="n">
         <f aca="false">INT((H26-Parámetros!$B$3)/7)+1</f>
         <v>8</v>
       </c>
-      <c r="K26" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="L26" s="18" t="n">
+      <c r="K26" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="L26" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M26" s="14" t="str">
+      <c r="M26" s="15" t="str">
         <f aca="false">IF(L26&gt;=1,"Completada",IF($M$3&lt;H26,"Pendiente",IF($M$3&gt;I26,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N26" s="19" t="str">
+      <c r="N26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=N$4,$H26&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O26" s="19" t="str">
+      <c r="O26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=O$4,$H26&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P26" s="19" t="str">
+      <c r="P26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=P$4,$H26&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q26" s="19" t="str">
+      <c r="Q26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=Q$4,$H26&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R26" s="19" t="str">
+      <c r="R26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=R$4,$H26&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S26" s="19" t="str">
+      <c r="S26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=S$4,$H26&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T26" s="19" t="str">
+      <c r="T26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=T$4,$H26&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U26" s="19" t="str">
+      <c r="U26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=U$4,$H26&lt;=U$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="V26" s="19" t="str">
+        <v>◆</v>
+      </c>
+      <c r="V26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=V$4,$H26&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W26" s="19" t="str">
+      <c r="W26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=W$4,$H26&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X26" s="19" t="str">
+      <c r="X26" s="20" t="str">
         <f aca="false">IF(AND($G26=0,$H26&gt;=X$4,$H26&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y26" s="19" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=Y$4,$H26&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="B27" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="B27" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C27" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="G27" s="16" t="n">
+      <c r="C27" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F27</f>
+        <v>46329</v>
+      </c>
+      <c r="I27" s="18" t="n">
+        <f aca="false">IF(G27=0,H27,H27+G27-1)</f>
+        <v>46340</v>
+      </c>
+      <c r="J27" s="15" t="n">
+        <f aca="false">INT((H27-Parámetros!$B$3)/7)+1</f>
         <v>6</v>
       </c>
-      <c r="H27" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F27</f>
-        <v>46348</v>
-      </c>
-      <c r="I27" s="17" t="n">
-        <f aca="false">IF(G27=0,H27,H27+G27-1)</f>
-        <v>46353</v>
-      </c>
-      <c r="J27" s="14" t="n">
-        <f aca="false">INT((H27-Parámetros!$B$3)/7)+1</f>
-        <v>8</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="L27" s="18" t="n">
+      <c r="K27" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L27" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M27" s="14" t="str">
+      <c r="M27" s="15" t="str">
         <f aca="false">IF(L27&gt;=1,"Completada",IF($M$3&lt;H27,"Pendiente",IF($M$3&gt;I27,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N27" s="19" t="str">
+      <c r="N27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=N$4,$H27&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O27" s="19" t="str">
+      <c r="O27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=O$4,$H27&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P27" s="19" t="str">
+      <c r="P27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=P$4,$H27&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q27" s="19" t="str">
+      <c r="Q27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=Q$4,$H27&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R27" s="19" t="str">
+      <c r="R27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=R$4,$H27&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S27" s="19" t="str">
+      <c r="S27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=S$4,$H27&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T27" s="19" t="str">
+      <c r="T27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=T$4,$H27&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U27" s="19" t="str">
+      <c r="U27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=U$4,$H27&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V27" s="19" t="str">
+      <c r="V27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=V$4,$H27&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W27" s="19" t="str">
+      <c r="W27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=W$4,$H27&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X27" s="19" t="str">
+      <c r="X27" s="20" t="str">
         <f aca="false">IF(AND($G27=0,$H27&gt;=X$4,$H27&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y27" s="19" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=Y$4,$H27&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="B28" s="14" t="n">
+        <v>107</v>
+      </c>
+      <c r="B28" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="16" t="s">
+      <c r="C28" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="G28" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="F28" s="16" t="n">
-        <v>57</v>
-      </c>
-      <c r="G28" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" s="17" t="n">
+      <c r="H28" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F28</f>
-        <v>46350</v>
-      </c>
-      <c r="I28" s="17" t="n">
+        <v>46331</v>
+      </c>
+      <c r="I28" s="18" t="n">
         <f aca="false">IF(G28=0,H28,H28+G28-1)</f>
-        <v>46356</v>
-      </c>
-      <c r="J28" s="14" t="n">
+        <v>46342</v>
+      </c>
+      <c r="J28" s="15" t="n">
         <f aca="false">INT((H28-Parámetros!$B$3)/7)+1</f>
-        <v>9</v>
-      </c>
-      <c r="K28" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L28" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M28" s="14" t="str">
+      <c r="M28" s="15" t="str">
         <f aca="false">IF(L28&gt;=1,"Completada",IF($M$3&lt;H28,"Pendiente",IF($M$3&gt;I28,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N28" s="19" t="str">
+      <c r="N28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=N$4,$H28&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O28" s="19" t="str">
+      <c r="O28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=O$4,$H28&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P28" s="19" t="str">
+      <c r="P28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=P$4,$H28&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q28" s="19" t="str">
+      <c r="Q28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=Q$4,$H28&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R28" s="19" t="str">
+      <c r="R28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=R$4,$H28&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S28" s="19" t="str">
+      <c r="S28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=S$4,$H28&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T28" s="19" t="str">
+      <c r="T28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=T$4,$H28&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U28" s="19" t="str">
+      <c r="U28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=U$4,$H28&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V28" s="19" t="str">
+      <c r="V28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=V$4,$H28&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W28" s="19" t="str">
+      <c r="W28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=W$4,$H28&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X28" s="19" t="str">
+      <c r="X28" s="20" t="str">
         <f aca="false">IF(AND($G28=0,$H28&gt;=X$4,$H28&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y28" s="19" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=Y$4,$H28&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="B29" s="14" t="n">
+        <v>109</v>
+      </c>
+      <c r="B29" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="G29" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="H29" s="17" t="n">
+      <c r="C29" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H29" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F29</f>
-        <v>46348</v>
-      </c>
-      <c r="I29" s="17" t="n">
+        <v>46338</v>
+      </c>
+      <c r="I29" s="18" t="n">
         <f aca="false">IF(G29=0,H29,H29+G29-1)</f>
-        <v>46356</v>
-      </c>
-      <c r="J29" s="14" t="n">
+        <v>46345</v>
+      </c>
+      <c r="J29" s="15" t="n">
         <f aca="false">INT((H29-Parámetros!$B$3)/7)+1</f>
-        <v>8</v>
-      </c>
-      <c r="K29" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="L29" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L29" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M29" s="14" t="str">
+      <c r="M29" s="15" t="str">
         <f aca="false">IF(L29&gt;=1,"Completada",IF($M$3&lt;H29,"Pendiente",IF($M$3&gt;I29,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N29" s="19" t="str">
+      <c r="N29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=N$4,$H29&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O29" s="19" t="str">
+      <c r="O29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=O$4,$H29&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P29" s="19" t="str">
+      <c r="P29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=P$4,$H29&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q29" s="19" t="str">
+      <c r="Q29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=Q$4,$H29&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R29" s="19" t="str">
+      <c r="R29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=R$4,$H29&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S29" s="19" t="str">
+      <c r="S29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=S$4,$H29&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T29" s="19" t="str">
+      <c r="T29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=T$4,$H29&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U29" s="19" t="str">
+      <c r="U29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=U$4,$H29&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V29" s="19" t="str">
+      <c r="V29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=V$4,$H29&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W29" s="19" t="str">
+      <c r="W29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=W$4,$H29&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X29" s="19" t="str">
+      <c r="X29" s="20" t="str">
         <f aca="false">IF(AND($G29=0,$H29&gt;=X$4,$H29&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y29" s="19" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=Y$4,$H29&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="B30" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="B30" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F30" s="16" t="n">
-        <v>61</v>
-      </c>
-      <c r="G30" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="H30" s="17" t="n">
+      <c r="C30" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H30" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F30</f>
-        <v>46354</v>
-      </c>
-      <c r="I30" s="17" t="n">
+        <v>46345</v>
+      </c>
+      <c r="I30" s="18" t="n">
         <f aca="false">IF(G30=0,H30,H30+G30-1)</f>
-        <v>46363</v>
-      </c>
-      <c r="J30" s="14" t="n">
+        <v>46349</v>
+      </c>
+      <c r="J30" s="15" t="n">
         <f aca="false">INT((H30-Parámetros!$B$3)/7)+1</f>
-        <v>9</v>
-      </c>
-      <c r="K30" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="L30" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="L30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M30" s="14" t="str">
+      <c r="M30" s="15" t="str">
         <f aca="false">IF(L30&gt;=1,"Completada",IF($M$3&lt;H30,"Pendiente",IF($M$3&gt;I30,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N30" s="19" t="str">
+      <c r="N30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=N$4,$H30&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O30" s="19" t="str">
+      <c r="O30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=O$4,$H30&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P30" s="19" t="str">
+      <c r="P30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=P$4,$H30&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q30" s="19" t="str">
+      <c r="Q30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=Q$4,$H30&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R30" s="19" t="str">
+      <c r="R30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=R$4,$H30&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S30" s="19" t="str">
+      <c r="S30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=S$4,$H30&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T30" s="19" t="str">
+      <c r="T30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=T$4,$H30&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U30" s="19" t="str">
+      <c r="U30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=U$4,$H30&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V30" s="19" t="str">
+      <c r="V30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=V$4,$H30&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W30" s="19" t="str">
+      <c r="W30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=W$4,$H30&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X30" s="19" t="str">
+      <c r="X30" s="20" t="str">
         <f aca="false">IF(AND($G30=0,$H30&gt;=X$4,$H30&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y30" s="19" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=Y$4,$H30&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="B31" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B31" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H31" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F31</f>
+        <v>46347</v>
+      </c>
+      <c r="I31" s="18" t="n">
+        <f aca="false">IF(G31=0,H31,H31+G31-1)</f>
+        <v>46351</v>
+      </c>
+      <c r="J31" s="15" t="n">
+        <f aca="false">INT((H31-Parámetros!$B$3)/7)+1</f>
+        <v>8</v>
+      </c>
+      <c r="K31" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F31" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="G31" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="H31" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F31</f>
-        <v>46361</v>
-      </c>
-      <c r="I31" s="17" t="n">
-        <f aca="false">IF(G31=0,H31,H31+G31-1)</f>
-        <v>46365</v>
-      </c>
-      <c r="J31" s="14" t="n">
-        <f aca="false">INT((H31-Parámetros!$B$3)/7)+1</f>
-        <v>10</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="L31" s="18" t="n">
+      <c r="L31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M31" s="14" t="str">
+      <c r="M31" s="15" t="str">
         <f aca="false">IF(L31&gt;=1,"Completada",IF($M$3&lt;H31,"Pendiente",IF($M$3&gt;I31,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N31" s="19" t="str">
+      <c r="N31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=N$4,$H31&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O31" s="19" t="str">
+      <c r="O31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=O$4,$H31&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P31" s="19" t="str">
+      <c r="P31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=P$4,$H31&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q31" s="19" t="str">
+      <c r="Q31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=Q$4,$H31&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R31" s="19" t="str">
+      <c r="R31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=R$4,$H31&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S31" s="19" t="str">
+      <c r="S31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=S$4,$H31&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T31" s="19" t="str">
+      <c r="T31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=T$4,$H31&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U31" s="19" t="str">
+      <c r="U31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=U$4,$H31&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V31" s="19" t="str">
+      <c r="V31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=V$4,$H31&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W31" s="19" t="str">
+      <c r="W31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=W$4,$H31&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X31" s="19" t="str">
+      <c r="X31" s="20" t="str">
         <f aca="false">IF(AND($G31=0,$H31&gt;=X$4,$H31&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-      <c r="Y31" s="19" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=Y$4,$H31&lt;=Y$4+6),"◆","")</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="B32" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <v>71</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="H32" s="17" t="n">
+      <c r="C32" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" s="18" t="n">
         <f aca="false">Parámetros!$B$3+F32</f>
-        <v>46364</v>
-      </c>
-      <c r="I32" s="17" t="n">
+        <v>46338</v>
+      </c>
+      <c r="I32" s="18" t="n">
         <f aca="false">IF(G32=0,H32,H32+G32-1)</f>
-        <v>46367</v>
-      </c>
-      <c r="J32" s="14" t="n">
+        <v>46347</v>
+      </c>
+      <c r="J32" s="15" t="n">
         <f aca="false">INT((H32-Parámetros!$B$3)/7)+1</f>
-        <v>11</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="L32" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="L32" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="M32" s="14" t="str">
+      <c r="M32" s="15" t="str">
         <f aca="false">IF(L32&gt;=1,"Completada",IF($M$3&lt;H32,"Pendiente",IF($M$3&gt;I32,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N32" s="19" t="str">
+      <c r="N32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=N$4,$H32&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O32" s="19" t="str">
+      <c r="O32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=O$4,$H32&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P32" s="19" t="str">
+      <c r="P32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=P$4,$H32&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q32" s="19" t="str">
+      <c r="Q32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=Q$4,$H32&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R32" s="19" t="str">
+      <c r="R32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=R$4,$H32&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S32" s="19" t="str">
+      <c r="S32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=S$4,$H32&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T32" s="19" t="str">
+      <c r="T32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=T$4,$H32&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U32" s="19" t="str">
+      <c r="U32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=U$4,$H32&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V32" s="19" t="str">
+      <c r="V32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=V$4,$H32&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W32" s="19" t="str">
+      <c r="W32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=W$4,$H32&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X32" s="19" t="str">
+      <c r="X32" s="20" t="str">
         <f aca="false">IF(AND($G32=0,$H32&gt;=X$4,$H32&lt;=X$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Y32" s="19" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=Y$4,$H32&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
-        <v>118</v>
-      </c>
-      <c r="B33" s="14" t="n">
+      <c r="A33" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B33" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <v>76</v>
-      </c>
-      <c r="G33" s="16" t="n">
+      <c r="C33" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F33</f>
+        <v>46346</v>
+      </c>
+      <c r="I33" s="18" t="n">
+        <f aca="false">IF(G33=0,H33,H33+G33-1)</f>
+        <v>46352</v>
+      </c>
+      <c r="J33" s="15" t="n">
+        <f aca="false">INT((H33-Parámetros!$B$3)/7)+1</f>
+        <v>8</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="17" t="n">
-        <f aca="false">Parámetros!$B$3+F33</f>
-        <v>46369</v>
-      </c>
-      <c r="I33" s="17" t="n">
-        <f aca="false">IF(G33=0,H33,H33+G33-1)</f>
-        <v>46369</v>
-      </c>
-      <c r="J33" s="14" t="n">
-        <f aca="false">INT((H33-Parámetros!$B$3)/7)+1</f>
-        <v>11</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="L33" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="14" t="str">
+      <c r="M33" s="15" t="str">
         <f aca="false">IF(L33&gt;=1,"Completada",IF($M$3&lt;H33,"Pendiente",IF($M$3&gt;I33,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="N33" s="19" t="str">
+      <c r="N33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=N$4,$H33&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="O33" s="19" t="str">
+      <c r="O33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=O$4,$H33&lt;=O$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="P33" s="19" t="str">
+      <c r="P33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=P$4,$H33&lt;=P$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="Q33" s="19" t="str">
+      <c r="Q33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=Q$4,$H33&lt;=Q$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="R33" s="19" t="str">
+      <c r="R33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=R$4,$H33&lt;=R$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="S33" s="19" t="str">
+      <c r="S33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=S$4,$H33&lt;=S$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="T33" s="19" t="str">
+      <c r="T33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=T$4,$H33&lt;=T$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="U33" s="19" t="str">
+      <c r="U33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=U$4,$H33&lt;=U$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="V33" s="19" t="str">
+      <c r="V33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=V$4,$H33&lt;=V$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="W33" s="19" t="str">
+      <c r="W33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=W$4,$H33&lt;=W$4+6),"◆","")</f>
         <v/>
       </c>
-      <c r="X33" s="19" t="str">
+      <c r="X33" s="20" t="str">
         <f aca="false">IF(AND($G33=0,$H33&gt;=X$4,$H33&lt;=X$4+6),"◆","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B34" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="H34" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F34</f>
+        <v>46351</v>
+      </c>
+      <c r="I34" s="18" t="n">
+        <f aca="false">IF(G34=0,H34,H34+G34-1)</f>
+        <v>46354</v>
+      </c>
+      <c r="J34" s="15" t="n">
+        <f aca="false">INT((H34-Parámetros!$B$3)/7)+1</f>
+        <v>9</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="L34" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="15" t="str">
+        <f aca="false">IF(L34&gt;=1,"Completada",IF($M$3&lt;H34,"Pendiente",IF($M$3&gt;I34,"Atrasada","En curso")))</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="N34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=N$4,$H34&lt;=N$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="O34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=O$4,$H34&lt;=O$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="P34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=P$4,$H34&lt;=P$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="Q34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=Q$4,$H34&lt;=Q$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="R34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=R$4,$H34&lt;=R$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="S34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=S$4,$H34&lt;=S$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="T34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=T$4,$H34&lt;=T$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="U34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=U$4,$H34&lt;=U$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="V34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=V$4,$H34&lt;=V$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="W34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=W$4,$H34&lt;=W$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="X34" s="20" t="str">
+        <f aca="false">IF(AND($G34=0,$H34&gt;=X$4,$H34&lt;=X$4+6),"◆","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <f aca="false">Parámetros!$B$3+F35</f>
+        <v>46354</v>
+      </c>
+      <c r="I35" s="18" t="n">
+        <f aca="false">IF(G35=0,H35,H35+G35-1)</f>
+        <v>46356</v>
+      </c>
+      <c r="J35" s="15" t="n">
+        <f aca="false">INT((H35-Parámetros!$B$3)/7)+1</f>
+        <v>9</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="L35" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="15" t="str">
+        <f aca="false">IF(L35&gt;=1,"Completada",IF($M$3&lt;H35,"Pendiente",IF($M$3&gt;I35,"Atrasada","En curso")))</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="N35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=N$4,$H35&lt;=N$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="O35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=O$4,$H35&lt;=O$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="P35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=P$4,$H35&lt;=P$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="Q35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=Q$4,$H35&lt;=Q$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="R35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=R$4,$H35&lt;=R$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="S35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=S$4,$H35&lt;=S$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="T35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=T$4,$H35&lt;=T$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="U35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=U$4,$H35&lt;=U$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="V35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=V$4,$H35&lt;=V$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="W35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=W$4,$H35&lt;=W$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="X35" s="20" t="str">
+        <f aca="false">IF(AND($G35=0,$H35&gt;=X$4,$H35&lt;=X$4+6),"◆","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <f aca="false">H36-Parámetros!$B$3</f>
+        <v>64</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="23" t="n">
+        <f aca="false">Parámetros!$B$12</f>
+        <v>46357</v>
+      </c>
+      <c r="I36" s="18" t="n">
+        <f aca="false">IF(G36=0,H36,H36+G36-1)</f>
+        <v>46357</v>
+      </c>
+      <c r="J36" s="15" t="n">
+        <f aca="false">INT((H36-Parámetros!$B$3)/7)+1</f>
+        <v>10</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="L36" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="15" t="str">
+        <f aca="false">IF(L36&gt;=1,"Completada",IF($M$3&lt;H36,"Pendiente",IF($M$3&gt;I36,"Atrasada","En curso")))</f>
+        <v>Pendiente</v>
+      </c>
+      <c r="N36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=N$4,$H36&lt;=N$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="O36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=O$4,$H36&lt;=O$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="P36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=P$4,$H36&lt;=P$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="Q36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=Q$4,$H36&lt;=Q$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="R36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=R$4,$H36&lt;=R$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="S36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=S$4,$H36&lt;=S$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="T36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=T$4,$H36&lt;=T$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="U36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=U$4,$H36&lt;=U$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="V36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=V$4,$H36&lt;=V$4+6),"◆","")</f>
+        <v/>
+      </c>
+      <c r="W36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=W$4,$H36&lt;=W$4+6),"◆","")</f>
         <v>◆</v>
       </c>
-      <c r="Y33" s="19" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=Y$4,$H33&lt;=Y$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22"/>
-      <c r="C36" s="6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="23"/>
-      <c r="C37" s="6" t="s">
-        <v>122</v>
+      <c r="X36" s="20" t="str">
+        <f aca="false">IF(AND($G36=0,$H36&gt;=X$4,$H36&lt;=X$4+6),"◆","")</f>
+        <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="24"/>
-      <c r="C38" s="6" t="s">
-        <v>123</v>
+      <c r="C38" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="25" t="s">
-        <v>124</v>
-      </c>
+      <c r="B39" s="24"/>
       <c r="C39" s="6" t="s">
-        <v>125</v>
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="25"/>
+      <c r="C40" s="6" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="26"/>
+      <c r="C41" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N6:Y33">
+  <conditionalFormatting sqref="N6:X36">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND($B6=1,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
     </cfRule>
@@ -4135,12 +4391,12 @@
       <formula>AND($M$3&gt;=N$4,$M$3&lt;=N$4+6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:Y4">
+  <conditionalFormatting sqref="N4:X4">
     <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>AND($M$3&gt;=N$4,$M$3&lt;=N$4+6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M33">
+  <conditionalFormatting sqref="M6:M36">
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>$M6="Completada"</formula>
     </cfRule>
@@ -4152,15 +4408,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Elija un nombre de la lista de la hoja Parámetros." errorStyle="stop" errorTitle="Responsable" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:E33" type="list">
-      <formula1>Parámetros!$A$10:$A$15</formula1>
+    <dataValidation allowBlank="true" error="Elija un nombre de la lista de la hoja Parámetros." errorStyle="stop" errorTitle="Responsable" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:E36" type="list">
+      <formula1>Parámetros!$A$15:$A$20</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Use un número entero de días (0 o más)." errorStyle="stop" errorTitle="Días" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F6:G33" type="whole">
+    <dataValidation allowBlank="false" error="Use un número entero de días (0 o más)." errorStyle="stop" errorTitle="Días" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F6:G15 F17:G25 F27:G35" type="whole">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Use un porcentaje entre 0 % y 100 %." errorStyle="stop" errorTitle="% avance" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L33" type="decimal">
+    <dataValidation allowBlank="false" error="Use un porcentaje entre 0 % y 100 %." errorStyle="stop" errorTitle="% avance" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L36" type="decimal">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -4180,7 +4436,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -4190,266 +4446,287 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="I3" s="12" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K3" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="28" t="n">
         <v>0.2</v>
       </c>
-      <c r="D4" s="17" t="n">
-        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$33,Cronograma!$B$6:$B$33,A4)</f>
+      <c r="D4" s="18" t="n">
+        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A4)</f>
         <v>46293</v>
       </c>
-      <c r="E4" s="17" t="n">
-        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$33,Cronograma!$B$6:$B$33,A4)</f>
-        <v>46306</v>
-      </c>
-      <c r="F4" s="14" t="n">
+      <c r="E4" s="18" t="n">
+        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A4)</f>
+        <v>46314</v>
+      </c>
+      <c r="F4" s="29" t="n">
         <f aca="false">E4-D4+1</f>
-        <v>14</v>
-      </c>
-      <c r="G4" s="14" t="n">
-        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$33,A4,Cronograma!$G$6:$G$33,"&gt;0")</f>
-        <v>8</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$33=A4)*Cronograma!$G$6:$G$33*Cronograma!$L$6:$L$33)/SUMIFS(Cronograma!$G$6:$G$33,Cronograma!$B$6:$B$33,A4),0)</f>
-        <v>0.957142857142857</v>
-      </c>
-      <c r="I4" s="14" t="str">
+        <v>22</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$36,A4,Cronograma!$G$6:$G$36,"&gt;0")</f>
+        <v>10</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A4)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A4),0)</f>
+        <v>0.790697674418605</v>
+      </c>
+      <c r="I4" s="15" t="str">
         <f aca="false">IF(H4&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D4,"Pendiente",IF(Parámetros!$B$4&gt;E4,"Atrasada","En curso")))</f>
         <v>En curso</v>
       </c>
-      <c r="J4" s="17" t="n">
-        <f aca="false">INDEX(Cronograma!$H$6:$H$33,MATCH("H"&amp;A4,Cronograma!$A$6:$A$33,0))</f>
-        <v>46306</v>
-      </c>
-      <c r="K4" s="14" t="n">
+      <c r="J4" s="23" t="n">
+        <f aca="false">Parámetros!$B$10</f>
+        <v>46314</v>
+      </c>
+      <c r="K4" s="29" t="n">
         <f aca="false">J4-Parámetros!$B$4</f>
+        <v>10</v>
+      </c>
+      <c r="L4" s="29" t="n">
+        <f aca="false">J4-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A4,Cronograma!$G$6:$G$36,"&gt;0")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="26" t="n">
+      <c r="B5" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="28" t="n">
         <v>0.1</v>
       </c>
-      <c r="D5" s="17" t="n">
-        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$33,Cronograma!$B$6:$B$33,A5)</f>
+      <c r="D5" s="18" t="n">
+        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A5)</f>
         <v>46307</v>
       </c>
-      <c r="E5" s="17" t="n">
-        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$33,Cronograma!$B$6:$B$33,A5)</f>
-        <v>46334</v>
-      </c>
-      <c r="F5" s="14" t="n">
+      <c r="E5" s="18" t="n">
+        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A5)</f>
+        <v>46345</v>
+      </c>
+      <c r="F5" s="29" t="n">
         <f aca="false">E5-D5+1</f>
-        <v>28</v>
-      </c>
-      <c r="G5" s="14" t="n">
-        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$33,A5,Cronograma!$G$6:$G$33,"&gt;0")</f>
-        <v>8</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$33=A5)*Cronograma!$G$6:$G$33*Cronograma!$L$6:$L$33)/SUMIFS(Cronograma!$G$6:$G$33,Cronograma!$B$6:$B$33,A5),0)</f>
+        <v>39</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$36,A5,Cronograma!$G$6:$G$36,"&gt;0")</f>
+        <v>9</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A5)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A5),0)</f>
         <v>0</v>
       </c>
-      <c r="I5" s="14" t="str">
+      <c r="I5" s="15" t="str">
         <f aca="false">IF(H5&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D5,"Pendiente",IF(Parámetros!$B$4&gt;E5,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="J5" s="17" t="n">
-        <f aca="false">INDEX(Cronograma!$H$6:$H$33,MATCH("H"&amp;A5,Cronograma!$A$6:$A$33,0))</f>
-        <v>46334</v>
-      </c>
-      <c r="K5" s="14" t="n">
+      <c r="J5" s="23" t="n">
+        <f aca="false">Parámetros!$B$11</f>
+        <v>46345</v>
+      </c>
+      <c r="K5" s="29" t="n">
         <f aca="false">J5-Parámetros!$B$4</f>
-        <v>30</v>
+        <v>41</v>
+      </c>
+      <c r="L5" s="29" t="n">
+        <f aca="false">J5-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A5,Cronograma!$G$6:$G$36,"&gt;0")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="26" t="n">
+      <c r="B6" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="28" t="n">
         <v>0.7</v>
       </c>
-      <c r="D6" s="17" t="n">
-        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$33,Cronograma!$B$6:$B$33,A6)</f>
-        <v>46335</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$33,Cronograma!$B$6:$B$33,A6)</f>
-        <v>46369</v>
-      </c>
-      <c r="F6" s="14" t="n">
+      <c r="D6" s="18" t="n">
+        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A6)</f>
+        <v>46329</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A6)</f>
+        <v>46357</v>
+      </c>
+      <c r="F6" s="29" t="n">
         <f aca="false">E6-D6+1</f>
-        <v>35</v>
-      </c>
-      <c r="G6" s="14" t="n">
-        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$33,A6,Cronograma!$G$6:$G$33,"&gt;0")</f>
+        <v>29</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$36,A6,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>9</v>
       </c>
-      <c r="H6" s="27" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$33=A6)*Cronograma!$G$6:$G$33*Cronograma!$L$6:$L$33)/SUMIFS(Cronograma!$G$6:$G$33,Cronograma!$B$6:$B$33,A6),0)</f>
+      <c r="H6" s="30" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A6)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A6),0)</f>
         <v>0</v>
       </c>
-      <c r="I6" s="14" t="str">
+      <c r="I6" s="15" t="str">
         <f aca="false">IF(H6&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D6,"Pendiente",IF(Parámetros!$B$4&gt;E6,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="J6" s="17" t="n">
-        <f aca="false">INDEX(Cronograma!$H$6:$H$33,MATCH("H"&amp;A6,Cronograma!$A$6:$A$33,0))</f>
-        <v>46369</v>
-      </c>
-      <c r="K6" s="14" t="n">
+      <c r="J6" s="23" t="n">
+        <f aca="false">Parámetros!$B$12</f>
+        <v>46357</v>
+      </c>
+      <c r="K6" s="29" t="n">
         <f aca="false">J6-Parámetros!$B$4</f>
-        <v>65</v>
+        <v>53</v>
+      </c>
+      <c r="L6" s="29" t="n">
+        <f aca="false">J6-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A6,Cronograma!$G$6:$G$36,"&gt;0")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="28" t="n">
+      <c r="B7" s="22" t="s">
+        <v>149</v>
+      </c>
+      <c r="C7" s="31" t="n">
         <f aca="false">SUM(C4:C6)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="32" t="n">
         <f aca="false">MIN(D4:D6)</f>
         <v>46293</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="32" t="n">
         <f aca="false">MAX(E4:E6)</f>
-        <v>46369</v>
-      </c>
-      <c r="F7" s="20" t="n">
+        <v>46357</v>
+      </c>
+      <c r="F7" s="33" t="n">
         <f aca="false">E7-D7+1</f>
-        <v>77</v>
-      </c>
-      <c r="G7" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="G7" s="34" t="n">
         <f aca="false">SUM(G4:G6)</f>
-        <v>25</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT(Cronograma!$G$6:$G$33,Cronograma!$L$6:$L$33)/SUM(Cronograma!$G$6:$G$33),0)</f>
-        <v>0.231034482758621</v>
+        <v>28</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <f aca="false">IFERROR(SUMPRODUCT(Cronograma!$G$6:$G$36,Cronograma!$L$6:$L$36)/SUM(Cronograma!$G$6:$G$36),0)</f>
+        <v>0.202380952380952</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H8" s="30" t="n">
+        <v>150</v>
+      </c>
+      <c r="H8" s="35" t="n">
         <f aca="false">SUMPRODUCT(C4:C6,H4:H6)</f>
-        <v>0.191428571428571</v>
+        <v>0.158139534883721</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$33,B11)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B11)</f>
+        <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="6" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$33,B12)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B12)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$33,B13)</f>
-        <v>20</v>
+        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B13)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$33,B14)</f>
+        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B14)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="C16" s="2" t="n">
         <f aca="false">SUM(C11:C14)</f>
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="L4:L6">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>$L4&lt;1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/entrega_1/docs/cronograma.xlsx
+++ b/entrega_1/docs/cronograma.xlsx
@@ -1,19 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\Proyecto_1_Innovacion_Tecnologica_IA_Grupo_4\entrega_1\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1876F21-333E-44A2-A535-807686BDFA86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Parámetros" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Cronograma" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Resumen" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Parámetros" sheetId="1" r:id="rId1"/>
+    <sheet name="Cronograma" sheetId="2" r:id="rId2"/>
+    <sheet name="Resumen" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,12 +36,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B3" authorId="0">
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -35,11 +49,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Inicio del proyecto: lunes 28/09/2026. Las actividades se calculan desde esta fecha.</t>
+          <t>Inicio del proyecto: lunes 28/09/2026. Las actividades se calculan desde esta fecha.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B4" authorId="0">
+    <comment ref="B4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -47,11 +61,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Por defecto es la fecha de hoy (=TODAY()). Escriba una fecha fija si quiere congelar el estado a un corte.</t>
+          <t>Por defecto es la fecha de hoy (=TODAY()). Escriba una fecha fija si quiere congelar el estado a un corte.</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -59,7 +73,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fechas oficiales del curso confirmadas por el equipo el 09/10/2026.</t>
+          <t>Fechas oficiales del curso confirmadas por el equipo el 09/10/2026.</t>
         </r>
       </text>
     </comment>
@@ -67,13 +81,13 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="C4" authorId="0">
+    <comment ref="C4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -81,11 +95,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fuente: documento 'Porcentajes de Evaluación' del curso (20 % / 10 % / 70 %).</t>
+          <t>Fuente: documento 'Porcentajes de Evaluación' del curso (20 % / 10 % / 70 %).</t>
         </r>
       </text>
     </comment>
-    <comment ref="C5" authorId="0">
+    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -93,11 +107,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fuente: documento 'Porcentajes de Evaluación' del curso (20 % / 10 % / 70 %).</t>
+          <t>Fuente: documento 'Porcentajes de Evaluación' del curso (20 % / 10 % / 70 %).</t>
         </r>
       </text>
     </comment>
-    <comment ref="C6" authorId="0">
+    <comment ref="C6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -105,7 +119,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fuente: documento 'Porcentajes de Evaluación' del curso (20 % / 10 % / 70 %).</t>
+          <t>Fuente: documento 'Porcentajes de Evaluación' del curso (20 % / 10 % / 70 %).</t>
         </r>
       </text>
     </comment>
@@ -116,492 +130,487 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="157">
   <si>
-    <t xml:space="preserve">Cronograma del proyecto — Identificación de especies por su canto (Grupo 4)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de inicio del proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de corte (seguimiento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de la última actividad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duración total del proyecto (días)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semana actual del proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fechas oficiales de entrega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega 1 (20 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega 2 (10 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega 3 (70 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipo (lista para la columna Responsable)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wilson Ospina Pérez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santiago Osorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martín Pérez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adriana Zapata</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todo el equipo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Por asignar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cómo usar este archivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Celdas con fondo amarillo y texto azul = datos de entrada: fechas de inicio y de entrega, desfase, duración, responsable y % de avance.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Las demás celdas se calculan con fórmulas: fechas, semana, estado, holgura, resumen por etapa y diagrama de Gantt.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Desfase = días desde la fecha de inicio hasta que empieza la actividad. Duración = días calendario. Los hitos toman la fecha oficial de esta hoja.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Estado: Completada (100 %), Pendiente (aún no inicia), En curso o Atrasada (pasó la fecha fin sin llegar al 100 %).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. En la hoja Resumen, la holgura debe ser de al menos 1 día: si es menor, la última actividad de la etapa termina tarde frente a la entrega.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plan de actividades y cronograma — Proyecto 1 · Innovación Tecnológica con IA · Grupo 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fechas calculadas desde la hoja Parámetros (inicio y fechas oficiales de entrega). Celdas amarillas = datos editables.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de corte:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etapa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actividad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entregable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Responsable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Desfase (días)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duración (días)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha inicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha fin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Predecesora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% avance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conformación del equipo y definición del tema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tema y repositorio creados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análisis del problema y árbol de problemas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secciones II y IV del reporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objetivos, alcance y pregunta de investigación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sección III del reporte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisión bibliográfica (estado del arte)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sección V.B y referencias</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análisis de soluciones existentes y brecha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secciones V.C a V.E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planeación: tareas, cronograma y riesgos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sección VII y cronograma.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estructura del repositorio y entorno de trabajo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carpeta entrega_1 en GitHub</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redacción del reporte 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borrador de docs/reporte_entrega_1.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3, 1.5, 1.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisión del reporte por el equipo y ajustes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comentarios incorporados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Versión final y publicación de la Entrega 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rama main actualizada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega 1: reporte de la primera etapa (20 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clave de API, metadatos de la región y selección de especies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lista de especies objetivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descarga de grabaciones y metadatos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/raw y metadatos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depuración y control de calidad de los datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conjunto depurado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Análisis exploratorio de datos (EDA)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notebook de EDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preprocesamiento: ventanas y espectrogramas Mel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">data/processed + índice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hipótesis y diseño experimental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sección de hipótesis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelos de referencia y CNN base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primeras métricas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Redacción del reporte 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reporte de la segunda etapa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6, 2.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisión y publicación de la Entrega 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carpeta entrega_2 en main</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega 2: reporte de la segunda etapa (10 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transferencia de aprendizaje con EfficientNet-B0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modelo entrenado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embeddings bioacústicos (BirdNET o Perch 2.0) + clasificador</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajuste de hiperparámetros y aumentación de datos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mejor configuración</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluación comparativa y análisis de errores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tablas y figuras de resultados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2, 3.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Validación con expertos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muestra revisada por expertos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prototipo de interfaz (Streamlit o Gradio)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicación de demostración</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reporte final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Video de 10 minutos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Video</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisión final y publicación en el repositorio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Repositorio final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7, 3.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega 3: reporte final y video (70 %)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Leyenda del Gantt:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etapa 1 · Planteamiento del problema</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etapa 2 · Datos y modelos de referencia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etapa 3 · Modelado, evaluación y comunicación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">◆</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Entrega oficial · columna gris = semana de la fecha de corte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resumen por etapa (calculado desde la hoja Cronograma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nombre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peso en la nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inicio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actividades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avance ponderado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha de entrega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Días para la entrega</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holgura antes de la entrega (días)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total del proyecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avance ponderado por peso en la nota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actividades por estado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En curso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pendiente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atrasada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total de filas (incluye hitos)</t>
+    <t>Cronograma del proyecto — Identificación de especies por su canto (Grupo 4)</t>
+  </si>
+  <si>
+    <t>Fecha de inicio del proyecto</t>
+  </si>
+  <si>
+    <t>Fecha de corte (seguimiento)</t>
+  </si>
+  <si>
+    <t>Fecha de la última actividad</t>
+  </si>
+  <si>
+    <t>Duración total del proyecto (días)</t>
+  </si>
+  <si>
+    <t>Semana actual del proyecto</t>
+  </si>
+  <si>
+    <t>Fechas oficiales de entrega</t>
+  </si>
+  <si>
+    <t>Entrega 1 (20 %)</t>
+  </si>
+  <si>
+    <t>Entrega 2 (10 %)</t>
+  </si>
+  <si>
+    <t>Entrega 3 (70 %)</t>
+  </si>
+  <si>
+    <t>Equipo (lista para la columna Responsable)</t>
+  </si>
+  <si>
+    <t>Wilson Ospina Pérez</t>
+  </si>
+  <si>
+    <t>Santiago Osorio</t>
+  </si>
+  <si>
+    <t>Martín Pérez</t>
+  </si>
+  <si>
+    <t>Adriana Zapata</t>
+  </si>
+  <si>
+    <t>Todo el equipo</t>
+  </si>
+  <si>
+    <t>Por asignar</t>
+  </si>
+  <si>
+    <t>Cómo usar este archivo</t>
+  </si>
+  <si>
+    <t>1. Celdas con fondo amarillo y texto azul = datos de entrada: fechas de inicio y de entrega, desfase, duración, responsable y % de avance.</t>
+  </si>
+  <si>
+    <t>2. Las demás celdas se calculan con fórmulas: fechas, semana, estado, holgura, resumen por etapa y diagrama de Gantt.</t>
+  </si>
+  <si>
+    <t>3. Desfase = días desde la fecha de inicio hasta que empieza la actividad. Duración = días calendario. Los hitos toman la fecha oficial de esta hoja.</t>
+  </si>
+  <si>
+    <t>4. Estado: Completada (100 %), Pendiente (aún no inicia), En curso o Atrasada (pasó la fecha fin sin llegar al 100 %).</t>
+  </si>
+  <si>
+    <t>5. En la hoja Resumen, la holgura debe ser de al menos 1 día: si es menor, la última actividad de la etapa termina tarde frente a la entrega.</t>
+  </si>
+  <si>
+    <t>Plan de actividades y cronograma — Proyecto 1 · Innovación Tecnológica con IA · Grupo 4</t>
+  </si>
+  <si>
+    <t>Fechas calculadas desde la hoja Parámetros (inicio y fechas oficiales de entrega). Celdas amarillas = datos editables.</t>
+  </si>
+  <si>
+    <t>Fecha de corte:</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>Actividad</t>
+  </si>
+  <si>
+    <t>Entregable</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Desfase (días)</t>
+  </si>
+  <si>
+    <t>Duración (días)</t>
+  </si>
+  <si>
+    <t>Fecha inicio</t>
+  </si>
+  <si>
+    <t>Fecha fin</t>
+  </si>
+  <si>
+    <t>Semana</t>
+  </si>
+  <si>
+    <t>Predecesora</t>
+  </si>
+  <si>
+    <t>% avance</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>1.1</t>
+  </si>
+  <si>
+    <t>Conformación del equipo y definición del tema</t>
+  </si>
+  <si>
+    <t>Tema y repositorio creados</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>Análisis del problema y árbol de problemas</t>
+  </si>
+  <si>
+    <t>Secciones II y IV del reporte</t>
+  </si>
+  <si>
+    <t>1.3</t>
+  </si>
+  <si>
+    <t>Objetivos, alcance y pregunta de investigación</t>
+  </si>
+  <si>
+    <t>Sección III del reporte</t>
+  </si>
+  <si>
+    <t>1.4</t>
+  </si>
+  <si>
+    <t>Revisión bibliográfica (estado del arte)</t>
+  </si>
+  <si>
+    <t>Sección V.B y referencias</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>Análisis de soluciones existentes y brecha</t>
+  </si>
+  <si>
+    <t>Secciones V.C a V.E</t>
+  </si>
+  <si>
+    <t>1.6</t>
+  </si>
+  <si>
+    <t>Planeación: tareas, cronograma y riesgos</t>
+  </si>
+  <si>
+    <t>Sección VII y cronograma.xlsx</t>
+  </si>
+  <si>
+    <t>1.7</t>
+  </si>
+  <si>
+    <t>Estructura del repositorio y entorno de trabajo</t>
+  </si>
+  <si>
+    <t>Carpeta entrega_1 en GitHub</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>Redacción del reporte 1</t>
+  </si>
+  <si>
+    <t>Borrador de docs/reporte_entrega_1.md</t>
+  </si>
+  <si>
+    <t>1.3, 1.5, 1.6</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>Revisión del reporte por el equipo y ajustes</t>
+  </si>
+  <si>
+    <t>Comentarios incorporados</t>
+  </si>
+  <si>
+    <t>1.10</t>
+  </si>
+  <si>
+    <t>Versión final y publicación de la Entrega 1</t>
+  </si>
+  <si>
+    <t>Rama main actualizada</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>Entrega 1: reporte de la primera etapa (20 %)</t>
+  </si>
+  <si>
+    <t>Hito</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>Clave de API, metadatos de la región y selección de especies</t>
+  </si>
+  <si>
+    <t>Lista de especies objetivo</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>Descarga de grabaciones y metadatos</t>
+  </si>
+  <si>
+    <t>data/raw y metadatos</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Depuración y control de calidad de los datos</t>
+  </si>
+  <si>
+    <t>Conjunto depurado</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>Análisis exploratorio de datos (EDA)</t>
+  </si>
+  <si>
+    <t>Notebook de EDA</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>Preprocesamiento: ventanas y espectrogramas Mel</t>
+  </si>
+  <si>
+    <t>data/processed + índice</t>
+  </si>
+  <si>
+    <t>2.6</t>
+  </si>
+  <si>
+    <t>Hipótesis y diseño experimental</t>
+  </si>
+  <si>
+    <t>Sección de hipótesis</t>
+  </si>
+  <si>
+    <t>2.7</t>
+  </si>
+  <si>
+    <t>Modelos de referencia y CNN base</t>
+  </si>
+  <si>
+    <t>Primeras métricas</t>
+  </si>
+  <si>
+    <t>2.8</t>
+  </si>
+  <si>
+    <t>Redacción del reporte 2</t>
+  </si>
+  <si>
+    <t>Reporte de la segunda etapa</t>
+  </si>
+  <si>
+    <t>2.6, 2.7</t>
+  </si>
+  <si>
+    <t>2.9</t>
+  </si>
+  <si>
+    <t>Revisión y publicación de la Entrega 2</t>
+  </si>
+  <si>
+    <t>Carpeta entrega_2 en main</t>
+  </si>
+  <si>
+    <t>H2</t>
+  </si>
+  <si>
+    <t>Entrega 2: reporte de la segunda etapa (10 %)</t>
+  </si>
+  <si>
+    <t>3.1</t>
+  </si>
+  <si>
+    <t>Transferencia de aprendizaje con EfficientNet-B0</t>
+  </si>
+  <si>
+    <t>Modelo entrenado</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>Embeddings bioacústicos (BirdNET o Perch 2.0) + clasificador</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Ajuste de hiperparámetros y aumentación de datos</t>
+  </si>
+  <si>
+    <t>Mejor configuración</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>Evaluación comparativa y análisis de errores</t>
+  </si>
+  <si>
+    <t>Tablas y figuras de resultados</t>
+  </si>
+  <si>
+    <t>3.2, 3.3</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>Validación con expertos</t>
+  </si>
+  <si>
+    <t>Muestra revisada por expertos</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>Prototipo de interfaz (Streamlit o Gradio)</t>
+  </si>
+  <si>
+    <t>Aplicación de demostración</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>Reporte final</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>Video de 10 minutos</t>
+  </si>
+  <si>
+    <t>Video</t>
+  </si>
+  <si>
+    <t>3.9</t>
+  </si>
+  <si>
+    <t>Revisión final y publicación en el repositorio</t>
+  </si>
+  <si>
+    <t>Repositorio final</t>
+  </si>
+  <si>
+    <t>3.7, 3.8</t>
+  </si>
+  <si>
+    <t>H3</t>
+  </si>
+  <si>
+    <t>Entrega 3: reporte final y video (70 %)</t>
+  </si>
+  <si>
+    <t>Leyenda del Gantt:</t>
+  </si>
+  <si>
+    <t>Etapa 1 · Planteamiento del problema</t>
+  </si>
+  <si>
+    <t>Etapa 2 · Datos y modelos de referencia</t>
+  </si>
+  <si>
+    <t>Etapa 3 · Modelado, evaluación y comunicación</t>
+  </si>
+  <si>
+    <t>◆</t>
+  </si>
+  <si>
+    <t>Entrega oficial · columna gris = semana de la fecha de corte</t>
+  </si>
+  <si>
+    <t>Resumen por etapa (calculado desde la hoja Cronograma)</t>
+  </si>
+  <si>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Peso en la nota</t>
+  </si>
+  <si>
+    <t>Inicio</t>
+  </si>
+  <si>
+    <t>Fin</t>
+  </si>
+  <si>
+    <t>Actividades</t>
+  </si>
+  <si>
+    <t>Avance ponderado</t>
+  </si>
+  <si>
+    <t>Fecha de entrega</t>
+  </si>
+  <si>
+    <t>Días para la entrega</t>
+  </si>
+  <si>
+    <t>Holgura antes de la entrega (días)</t>
+  </si>
+  <si>
+    <t>Total del proyecto</t>
+  </si>
+  <si>
+    <t>Avance ponderado por peso en la nota</t>
+  </si>
+  <si>
+    <t>Actividades por estado</t>
+  </si>
+  <si>
+    <t>Completada</t>
+  </si>
+  <si>
+    <t>En curso</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t>Atrasada</t>
+  </si>
+  <si>
+    <t>Total de filas (incluye hitos)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0"/>
-    <numFmt numFmtId="167" formatCode="dd/mm"/>
-    <numFmt numFmtId="168" formatCode="\S0"/>
-    <numFmt numFmtId="169" formatCode="@"/>
-    <numFmt numFmtId="170" formatCode="0%"/>
-    <numFmt numFmtId="171" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm"/>
+    <numFmt numFmtId="166" formatCode="\S0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -610,46 +619,27 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <color rgb="FF1B4332"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -658,49 +648,43 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="13"/>
       <color rgb="FF1B4332"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color rgb="FFC1121F"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -743,14 +727,14 @@
     </fill>
   </fills>
   <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -765,7 +749,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="hair">
         <color rgb="FFD9D9D9"/>
       </left>
@@ -781,190 +765,117 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="36">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="166" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFE9C46A"/>
+          <bgColor rgb="FFF8C4C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEDEDED"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF8E7DBE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -978,27 +889,20 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF8E7DBE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEDEDED"/>
+          <bgColor rgb="FFE9C46A"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <font>
-        <b val="1"/>
+        <b/>
         <color rgb="FFC1121F"/>
       </font>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFC7E9C0"/>
+          <bgColor rgb="FFF8C4C4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1012,11 +916,12 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFF8C4C4"/>
+          <bgColor rgb="FFC7E9C0"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -1075,47 +980,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1B4332"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1123,12 +1044,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1157,7 +1078,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1178,7 +1099,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1229,7 +1150,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1247,269 +1168,259 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="3">
         <v>46293</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <f aca="true">TODAY()</f>
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4">
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="n">
-        <f aca="false">MAX(Cronograma!$I$6:$I$36)</f>
+      <c r="B5" s="4">
+        <f>MAX(Cronograma!$I$6:$I$36)</f>
         <v>46357</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <f aca="false">B5-B3+1</f>
+      <c r="B6" s="5">
+        <f>B5-B3+1</f>
         <v>65</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="n">
-        <f aca="false">IF(B4&lt;B3,0,INT((B4-B3)/7)+1)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5">
+        <f>IF(B4&lt;B3,0,INT((B4-B3)/7)+1)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="3">
         <v>46314</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="3">
         <v>46345</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="3">
         <v>46357</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>22</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X42"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="14" style="0" width="6.51"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="7" customWidth="1"/>
+    <col min="3" max="3" width="50" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="7" width="9" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="24" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:24" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="L3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="10" t="n">
-        <f aca="false">Parámetros!$B$4</f>
-        <v>46304</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(N$5-1)</f>
+      <c r="M3" s="10">
+        <f>Parámetros!$B$4</f>
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="N4" s="11">
+        <f>Parámetros!$B$3+7*(N$5-1)</f>
         <v>46293</v>
       </c>
-      <c r="O4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(O$5-1)</f>
+      <c r="O4" s="11">
+        <f>Parámetros!$B$3+7*(O$5-1)</f>
         <v>46300</v>
       </c>
-      <c r="P4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(P$5-1)</f>
+      <c r="P4" s="11">
+        <f>Parámetros!$B$3+7*(P$5-1)</f>
         <v>46307</v>
       </c>
-      <c r="Q4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(Q$5-1)</f>
+      <c r="Q4" s="11">
+        <f>Parámetros!$B$3+7*(Q$5-1)</f>
         <v>46314</v>
       </c>
-      <c r="R4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(R$5-1)</f>
+      <c r="R4" s="11">
+        <f>Parámetros!$B$3+7*(R$5-1)</f>
         <v>46321</v>
       </c>
-      <c r="S4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(S$5-1)</f>
+      <c r="S4" s="11">
+        <f>Parámetros!$B$3+7*(S$5-1)</f>
         <v>46328</v>
       </c>
-      <c r="T4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(T$5-1)</f>
+      <c r="T4" s="11">
+        <f>Parámetros!$B$3+7*(T$5-1)</f>
         <v>46335</v>
       </c>
-      <c r="U4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(U$5-1)</f>
+      <c r="U4" s="11">
+        <f>Parámetros!$B$3+7*(U$5-1)</f>
         <v>46342</v>
       </c>
-      <c r="V4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(V$5-1)</f>
+      <c r="V4" s="11">
+        <f>Parámetros!$B$3+7*(V$5-1)</f>
         <v>46349</v>
       </c>
-      <c r="W4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(W$5-1)</f>
+      <c r="W4" s="11">
+        <f>Parámetros!$B$3+7*(W$5-1)</f>
         <v>46356</v>
       </c>
-      <c r="X4" s="11" t="n">
-        <f aca="false">Parámetros!$B$3+7*(X$5-1)</f>
+      <c r="X4" s="11">
+        <f>Parámetros!$B$3+7*(X$5-1)</f>
         <v>46363</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:24" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>26</v>
       </c>
@@ -1549,45 +1460,45 @@
       <c r="M5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="N5" s="13" t="n">
+      <c r="N5" s="13">
         <v>1</v>
       </c>
-      <c r="O5" s="13" t="n">
+      <c r="O5" s="13">
         <v>2</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="13">
         <v>3</v>
       </c>
-      <c r="Q5" s="13" t="n">
+      <c r="Q5" s="13">
         <v>4</v>
       </c>
-      <c r="R5" s="13" t="n">
+      <c r="R5" s="13">
         <v>5</v>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="13">
         <v>6</v>
       </c>
-      <c r="T5" s="13" t="n">
+      <c r="T5" s="13">
         <v>7</v>
       </c>
-      <c r="U5" s="13" t="n">
+      <c r="U5" s="13">
         <v>8</v>
       </c>
-      <c r="V5" s="13" t="n">
+      <c r="V5" s="13">
         <v>9</v>
       </c>
-      <c r="W5" s="13" t="n">
+      <c r="W5" s="13">
         <v>10</v>
       </c>
-      <c r="X5" s="13" t="n">
+      <c r="X5" s="13">
         <v>11</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="15" t="n">
+      <c r="B6" s="15">
         <v>1</v>
       </c>
       <c r="C6" s="16" t="s">
@@ -1599,84 +1510,84 @@
       <c r="E6" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="17">
         <v>0</v>
       </c>
-      <c r="G6" s="17" t="n">
+      <c r="G6" s="17">
         <v>3</v>
       </c>
-      <c r="H6" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F6</f>
+      <c r="H6" s="18">
+        <f>Parámetros!$B$3+F6</f>
         <v>46293</v>
       </c>
-      <c r="I6" s="18" t="n">
-        <f aca="false">IF(G6=0,H6,H6+G6-1)</f>
+      <c r="I6" s="18">
+        <f t="shared" ref="I6:I36" si="0">IF(G6=0,H6,H6+G6-1)</f>
         <v>46295</v>
       </c>
-      <c r="J6" s="15" t="n">
-        <f aca="false">INT((H6-Parámetros!$B$3)/7)+1</f>
+      <c r="J6" s="15">
+        <f>INT((H6-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
       <c r="K6" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="19" t="n">
+      <c r="L6" s="19">
         <v>1</v>
       </c>
       <c r="M6" s="15" t="str">
-        <f aca="false">IF(L6&gt;=1,"Completada",IF($M$3&lt;H6,"Pendiente",IF($M$3&gt;I6,"Atrasada","En curso")))</f>
+        <f t="shared" ref="M6:M36" si="1">IF(L6&gt;=1,"Completada",IF($M$3&lt;H6,"Pendiente",IF($M$3&gt;I6,"Atrasada","En curso")))</f>
         <v>Completada</v>
       </c>
       <c r="N6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=N$4,$H6&lt;=N$4+6),"◆","")</f>
+        <f t="shared" ref="N6:X15" si="2">IF(AND($G6=0,$H6&gt;=N$4,$H6&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
       <c r="O6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=O$4,$H6&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=P$4,$H6&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=Q$4,$H6&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=R$4,$H6&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=S$4,$H6&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=T$4,$H6&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=U$4,$H6&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=V$4,$H6&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=W$4,$H6&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X6" s="20" t="str">
-        <f aca="false">IF(AND($G6=0,$H6&gt;=X$4,$H6&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="15">
         <v>1</v>
       </c>
       <c r="C7" s="16" t="s">
@@ -1688,84 +1599,84 @@
       <c r="E7" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="17">
         <v>2</v>
       </c>
-      <c r="G7" s="17" t="n">
+      <c r="G7" s="17">
         <v>6</v>
       </c>
-      <c r="H7" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F7</f>
+      <c r="H7" s="18">
+        <f>Parámetros!$B$3+F7</f>
         <v>46295</v>
       </c>
-      <c r="I7" s="18" t="n">
-        <f aca="false">IF(G7=0,H7,H7+G7-1)</f>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="J7" s="15" t="n">
-        <f aca="false">INT((H7-Parámetros!$B$3)/7)+1</f>
+      <c r="J7" s="15">
+        <f>INT((H7-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="19" t="n">
+      <c r="L7" s="19">
         <v>1</v>
       </c>
       <c r="M7" s="15" t="str">
-        <f aca="false">IF(L7&gt;=1,"Completada",IF($M$3&lt;H7,"Pendiente",IF($M$3&gt;I7,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=N$4,$H7&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=O$4,$H7&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=P$4,$H7&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=Q$4,$H7&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=R$4,$H7&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=S$4,$H7&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=T$4,$H7&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=U$4,$H7&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=V$4,$H7&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=W$4,$H7&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X7" s="20" t="str">
-        <f aca="false">IF(AND($G7=0,$H7&gt;=X$4,$H7&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="15">
         <v>1</v>
       </c>
       <c r="C8" s="16" t="s">
@@ -1777,84 +1688,84 @@
       <c r="E8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="17">
         <v>5</v>
       </c>
-      <c r="G8" s="17" t="n">
+      <c r="G8" s="17">
         <v>4</v>
       </c>
-      <c r="H8" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F8</f>
+      <c r="H8" s="18">
+        <f>Parámetros!$B$3+F8</f>
         <v>46298</v>
       </c>
-      <c r="I8" s="18" t="n">
-        <f aca="false">IF(G8=0,H8,H8+G8-1)</f>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
         <v>46301</v>
       </c>
-      <c r="J8" s="15" t="n">
-        <f aca="false">INT((H8-Parámetros!$B$3)/7)+1</f>
+      <c r="J8" s="15">
+        <f>INT((H8-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="19" t="n">
+      <c r="L8" s="19">
         <v>1</v>
       </c>
       <c r="M8" s="15" t="str">
-        <f aca="false">IF(L8&gt;=1,"Completada",IF($M$3&lt;H8,"Pendiente",IF($M$3&gt;I8,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=N$4,$H8&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=O$4,$H8&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=P$4,$H8&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=Q$4,$H8&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=R$4,$H8&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=S$4,$H8&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=T$4,$H8&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=U$4,$H8&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=V$4,$H8&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=W$4,$H8&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X8" s="20" t="str">
-        <f aca="false">IF(AND($G8=0,$H8&gt;=X$4,$H8&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="15">
         <v>1</v>
       </c>
       <c r="C9" s="16" t="s">
@@ -1866,84 +1777,84 @@
       <c r="E9" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="17" t="n">
+      <c r="F9" s="17">
         <v>2</v>
       </c>
-      <c r="G9" s="17" t="n">
+      <c r="G9" s="17">
         <v>9</v>
       </c>
-      <c r="H9" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F9</f>
+      <c r="H9" s="18">
+        <f>Parámetros!$B$3+F9</f>
         <v>46295</v>
       </c>
-      <c r="I9" s="18" t="n">
-        <f aca="false">IF(G9=0,H9,H9+G9-1)</f>
+      <c r="I9" s="18">
+        <f t="shared" si="0"/>
         <v>46303</v>
       </c>
-      <c r="J9" s="15" t="n">
-        <f aca="false">INT((H9-Parámetros!$B$3)/7)+1</f>
+      <c r="J9" s="15">
+        <f>INT((H9-Parámetros!$B$3)/7)+1</f>
         <v>1</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="19" t="n">
+      <c r="L9" s="19">
         <v>1</v>
       </c>
       <c r="M9" s="15" t="str">
-        <f aca="false">IF(L9&gt;=1,"Completada",IF($M$3&lt;H9,"Pendiente",IF($M$3&gt;I9,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=N$4,$H9&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=O$4,$H9&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=P$4,$H9&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=Q$4,$H9&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=R$4,$H9&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=S$4,$H9&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=T$4,$H9&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=U$4,$H9&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=V$4,$H9&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=W$4,$H9&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X9" s="20" t="str">
-        <f aca="false">IF(AND($G9=0,$H9&gt;=X$4,$H9&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="15">
         <v>1</v>
       </c>
       <c r="C10" s="16" t="s">
@@ -1955,84 +1866,84 @@
       <c r="E10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="17">
         <v>7</v>
       </c>
-      <c r="G10" s="17" t="n">
+      <c r="G10" s="17">
         <v>4</v>
       </c>
-      <c r="H10" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F10</f>
+      <c r="H10" s="18">
+        <f>Parámetros!$B$3+F10</f>
         <v>46300</v>
       </c>
-      <c r="I10" s="18" t="n">
-        <f aca="false">IF(G10=0,H10,H10+G10-1)</f>
+      <c r="I10" s="18">
+        <f t="shared" si="0"/>
         <v>46303</v>
       </c>
-      <c r="J10" s="15" t="n">
-        <f aca="false">INT((H10-Parámetros!$B$3)/7)+1</f>
+      <c r="J10" s="15">
+        <f>INT((H10-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="19" t="n">
+      <c r="L10" s="19">
         <v>1</v>
       </c>
       <c r="M10" s="15" t="str">
-        <f aca="false">IF(L10&gt;=1,"Completada",IF($M$3&lt;H10,"Pendiente",IF($M$3&gt;I10,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=N$4,$H10&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=O$4,$H10&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=P$4,$H10&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=Q$4,$H10&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=R$4,$H10&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=S$4,$H10&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=T$4,$H10&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=U$4,$H10&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=V$4,$H10&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=W$4,$H10&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X10" s="20" t="str">
-        <f aca="false">IF(AND($G10=0,$H10&gt;=X$4,$H10&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="15">
         <v>1</v>
       </c>
       <c r="C11" s="16" t="s">
@@ -2044,84 +1955,84 @@
       <c r="E11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="17" t="n">
+      <c r="F11" s="17">
         <v>8</v>
       </c>
-      <c r="G11" s="17" t="n">
+      <c r="G11" s="17">
         <v>3</v>
       </c>
-      <c r="H11" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F11</f>
+      <c r="H11" s="18">
+        <f>Parámetros!$B$3+F11</f>
         <v>46301</v>
       </c>
-      <c r="I11" s="18" t="n">
-        <f aca="false">IF(G11=0,H11,H11+G11-1)</f>
+      <c r="I11" s="18">
+        <f t="shared" si="0"/>
         <v>46303</v>
       </c>
-      <c r="J11" s="15" t="n">
-        <f aca="false">INT((H11-Parámetros!$B$3)/7)+1</f>
+      <c r="J11" s="15">
+        <f>INT((H11-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="L11" s="19" t="n">
+      <c r="L11" s="19">
         <v>1</v>
       </c>
       <c r="M11" s="15" t="str">
-        <f aca="false">IF(L11&gt;=1,"Completada",IF($M$3&lt;H11,"Pendiente",IF($M$3&gt;I11,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=N$4,$H11&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=O$4,$H11&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=P$4,$H11&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=Q$4,$H11&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=R$4,$H11&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=S$4,$H11&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=T$4,$H11&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=U$4,$H11&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=V$4,$H11&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=W$4,$H11&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X11" s="20" t="str">
-        <f aca="false">IF(AND($G11=0,$H11&gt;=X$4,$H11&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="15">
         <v>1</v>
       </c>
       <c r="C12" s="16" t="s">
@@ -2133,84 +2044,84 @@
       <c r="E12" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="17">
         <v>9</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="17">
         <v>3</v>
       </c>
-      <c r="H12" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F12</f>
+      <c r="H12" s="18">
+        <f>Parámetros!$B$3+F12</f>
         <v>46302</v>
       </c>
-      <c r="I12" s="18" t="n">
-        <f aca="false">IF(G12=0,H12,H12+G12-1)</f>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
         <v>46304</v>
       </c>
-      <c r="J12" s="15" t="n">
-        <f aca="false">INT((H12-Parámetros!$B$3)/7)+1</f>
+      <c r="J12" s="15">
+        <f>INT((H12-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="L12" s="19" t="n">
+      <c r="L12" s="19">
         <v>1</v>
       </c>
       <c r="M12" s="15" t="str">
-        <f aca="false">IF(L12&gt;=1,"Completada",IF($M$3&lt;H12,"Pendiente",IF($M$3&gt;I12,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=N$4,$H12&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=O$4,$H12&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=P$4,$H12&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=Q$4,$H12&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=R$4,$H12&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=S$4,$H12&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=T$4,$H12&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=U$4,$H12&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=V$4,$H12&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=W$4,$H12&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X12" s="20" t="str">
-        <f aca="false">IF(AND($G12=0,$H12&gt;=X$4,$H12&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="15">
         <v>1</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -2222,84 +2133,84 @@
       <c r="E13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="17">
         <v>10</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="17">
         <v>2</v>
       </c>
-      <c r="H13" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F13</f>
+      <c r="H13" s="18">
+        <f>Parámetros!$B$3+F13</f>
         <v>46303</v>
       </c>
-      <c r="I13" s="18" t="n">
-        <f aca="false">IF(G13=0,H13,H13+G13-1)</f>
+      <c r="I13" s="18">
+        <f t="shared" si="0"/>
         <v>46304</v>
       </c>
-      <c r="J13" s="15" t="n">
-        <f aca="false">INT((H13-Parámetros!$B$3)/7)+1</f>
+      <c r="J13" s="15">
+        <f>INT((H13-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L13" s="19" t="n">
+      <c r="L13" s="19">
         <v>1</v>
       </c>
       <c r="M13" s="15" t="str">
-        <f aca="false">IF(L13&gt;=1,"Completada",IF($M$3&lt;H13,"Pendiente",IF($M$3&gt;I13,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Completada</v>
       </c>
       <c r="N13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=N$4,$H13&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=O$4,$H13&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=P$4,$H13&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=Q$4,$H13&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=R$4,$H13&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=S$4,$H13&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=T$4,$H13&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=U$4,$H13&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=V$4,$H13&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=W$4,$H13&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X13" s="20" t="str">
-        <f aca="false">IF(AND($G13=0,$H13&gt;=X$4,$H13&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="15">
         <v>1</v>
       </c>
       <c r="C14" s="16" t="s">
@@ -2311,84 +2222,84 @@
       <c r="E14" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="17">
         <v>12</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="17">
         <v>6</v>
       </c>
-      <c r="H14" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F14</f>
+      <c r="H14" s="18">
+        <f>Parámetros!$B$3+F14</f>
         <v>46305</v>
       </c>
-      <c r="I14" s="18" t="n">
-        <f aca="false">IF(G14=0,H14,H14+G14-1)</f>
+      <c r="I14" s="18">
+        <f t="shared" si="0"/>
         <v>46310</v>
       </c>
-      <c r="J14" s="15" t="n">
-        <f aca="false">INT((H14-Parámetros!$B$3)/7)+1</f>
+      <c r="J14" s="15">
+        <f>INT((H14-Parámetros!$B$3)/7)+1</f>
         <v>2</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="L14" s="19" t="n">
-        <v>0</v>
+      <c r="L14" s="19">
+        <v>1</v>
       </c>
       <c r="M14" s="15" t="str">
-        <f aca="false">IF(L14&gt;=1,"Completada",IF($M$3&lt;H14,"Pendiente",IF($M$3&gt;I14,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
+        <f t="shared" si="1"/>
+        <v>Completada</v>
       </c>
       <c r="N14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=N$4,$H14&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=O$4,$H14&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=P$4,$H14&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=Q$4,$H14&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=R$4,$H14&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=S$4,$H14&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=T$4,$H14&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=U$4,$H14&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=V$4,$H14&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=W$4,$H14&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X14" s="20" t="str">
-        <f aca="false">IF(AND($G14=0,$H14&gt;=X$4,$H14&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="15" t="n">
+      <c r="B15" s="15">
         <v>1</v>
       </c>
       <c r="C15" s="16" t="s">
@@ -2400,84 +2311,84 @@
       <c r="E15" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="17" t="n">
+      <c r="F15" s="17">
         <v>18</v>
       </c>
-      <c r="G15" s="17" t="n">
+      <c r="G15" s="17">
         <v>3</v>
       </c>
-      <c r="H15" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F15</f>
+      <c r="H15" s="18">
+        <f>Parámetros!$B$3+F15</f>
         <v>46311</v>
       </c>
-      <c r="I15" s="18" t="n">
-        <f aca="false">IF(G15=0,H15,H15+G15-1)</f>
+      <c r="I15" s="18">
+        <f t="shared" si="0"/>
         <v>46313</v>
       </c>
-      <c r="J15" s="15" t="n">
-        <f aca="false">INT((H15-Parámetros!$B$3)/7)+1</f>
+      <c r="J15" s="15">
+        <f>INT((H15-Parámetros!$B$3)/7)+1</f>
         <v>3</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L15" s="19" t="n">
-        <v>0</v>
+      <c r="L15" s="19">
+        <v>1</v>
       </c>
       <c r="M15" s="15" t="str">
-        <f aca="false">IF(L15&gt;=1,"Completada",IF($M$3&lt;H15,"Pendiente",IF($M$3&gt;I15,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
+        <f t="shared" si="1"/>
+        <v>Completada</v>
       </c>
       <c r="N15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=N$4,$H15&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="O15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=O$4,$H15&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="P15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=P$4,$H15&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="Q15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=Q$4,$H15&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="R15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=R$4,$H15&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="S15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=S$4,$H15&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="T15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=T$4,$H15&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="U15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=U$4,$H15&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="V15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=V$4,$H15&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="W15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=W$4,$H15&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="X15" s="20" t="str">
-        <f aca="false">IF(AND($G15=0,$H15&gt;=X$4,$H15&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B16" s="15">
         <v>1</v>
       </c>
       <c r="C16" s="22" t="s">
@@ -2489,85 +2400,85 @@
       <c r="E16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="15" t="n">
-        <f aca="false">H16-Parámetros!$B$3</f>
+      <c r="F16" s="15">
+        <f>H16-Parámetros!$B$3</f>
         <v>21</v>
       </c>
-      <c r="G16" s="15" t="n">
+      <c r="G16" s="15">
         <v>0</v>
       </c>
-      <c r="H16" s="23" t="n">
-        <f aca="false">Parámetros!$B$10</f>
+      <c r="H16" s="23">
+        <f>Parámetros!$B$10</f>
         <v>46314</v>
       </c>
-      <c r="I16" s="18" t="n">
-        <f aca="false">IF(G16=0,H16,H16+G16-1)</f>
+      <c r="I16" s="18">
+        <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-      <c r="J16" s="15" t="n">
-        <f aca="false">INT((H16-Parámetros!$B$3)/7)+1</f>
+      <c r="J16" s="15">
+        <f>INT((H16-Parámetros!$B$3)/7)+1</f>
         <v>4</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="L16" s="19" t="n">
-        <v>0</v>
+      <c r="L16" s="19">
+        <v>1</v>
       </c>
       <c r="M16" s="15" t="str">
-        <f aca="false">IF(L16&gt;=1,"Completada",IF($M$3&lt;H16,"Pendiente",IF($M$3&gt;I16,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
+        <f t="shared" si="1"/>
+        <v>Completada</v>
       </c>
       <c r="N16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=N$4,$H16&lt;=N$4+6),"◆","")</f>
+        <f t="shared" ref="N16:X25" si="3">IF(AND($G16=0,$H16&gt;=N$4,$H16&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
       <c r="O16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=O$4,$H16&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=P$4,$H16&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=Q$4,$H16&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v>◆</v>
       </c>
       <c r="R16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=R$4,$H16&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=S$4,$H16&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=T$4,$H16&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=U$4,$H16&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=V$4,$H16&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=W$4,$H16&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X16" s="20" t="str">
-        <f aca="false">IF(AND($G16=0,$H16&gt;=X$4,$H16&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B17" s="15">
         <v>2</v>
       </c>
       <c r="C17" s="16" t="s">
@@ -2579,84 +2490,84 @@
       <c r="E17" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F17" s="17">
         <v>14</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G17" s="17">
         <v>6</v>
       </c>
-      <c r="H17" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F17</f>
+      <c r="H17" s="18">
+        <f>Parámetros!$B$3+F17</f>
         <v>46307</v>
       </c>
-      <c r="I17" s="18" t="n">
-        <f aca="false">IF(G17=0,H17,H17+G17-1)</f>
+      <c r="I17" s="18">
+        <f t="shared" si="0"/>
         <v>46312</v>
       </c>
-      <c r="J17" s="15" t="n">
-        <f aca="false">INT((H17-Parámetros!$B$3)/7)+1</f>
+      <c r="J17" s="15">
+        <f>INT((H17-Parámetros!$B$3)/7)+1</f>
         <v>3</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="L17" s="19" t="n">
+      <c r="L17" s="19">
         <v>0</v>
       </c>
       <c r="M17" s="15" t="str">
-        <f aca="false">IF(L17&gt;=1,"Completada",IF($M$3&lt;H17,"Pendiente",IF($M$3&gt;I17,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
+        <f t="shared" si="1"/>
+        <v>Atrasada</v>
       </c>
       <c r="N17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=N$4,$H17&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=O$4,$H17&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=P$4,$H17&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=Q$4,$H17&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=R$4,$H17&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=S$4,$H17&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=T$4,$H17&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=U$4,$H17&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=V$4,$H17&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=W$4,$H17&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X17" s="20" t="str">
-        <f aca="false">IF(AND($G17=0,$H17&gt;=X$4,$H17&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B18" s="15">
         <v>2</v>
       </c>
       <c r="C18" s="16" t="s">
@@ -2668,84 +2579,84 @@
       <c r="E18" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="17">
         <v>18</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="17">
         <v>5</v>
       </c>
-      <c r="H18" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F18</f>
+      <c r="H18" s="18">
+        <f>Parámetros!$B$3+F18</f>
         <v>46311</v>
       </c>
-      <c r="I18" s="18" t="n">
-        <f aca="false">IF(G18=0,H18,H18+G18-1)</f>
+      <c r="I18" s="18">
+        <f t="shared" si="0"/>
         <v>46315</v>
       </c>
-      <c r="J18" s="15" t="n">
-        <f aca="false">INT((H18-Parámetros!$B$3)/7)+1</f>
+      <c r="J18" s="15">
+        <f>INT((H18-Parámetros!$B$3)/7)+1</f>
         <v>3</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="L18" s="19" t="n">
+      <c r="L18" s="19">
         <v>0</v>
       </c>
       <c r="M18" s="15" t="str">
-        <f aca="false">IF(L18&gt;=1,"Completada",IF($M$3&lt;H18,"Pendiente",IF($M$3&gt;I18,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
+        <f t="shared" si="1"/>
+        <v>En curso</v>
       </c>
       <c r="N18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=N$4,$H18&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=O$4,$H18&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=P$4,$H18&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=Q$4,$H18&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=R$4,$H18&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=S$4,$H18&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=T$4,$H18&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=U$4,$H18&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=V$4,$H18&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=W$4,$H18&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X18" s="20" t="str">
-        <f aca="false">IF(AND($G18=0,$H18&gt;=X$4,$H18&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="15">
         <v>2</v>
       </c>
       <c r="C19" s="16" t="s">
@@ -2757,84 +2668,84 @@
       <c r="E19" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="17">
         <v>21</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="17">
         <v>5</v>
       </c>
-      <c r="H19" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F19</f>
+      <c r="H19" s="18">
+        <f>Parámetros!$B$3+F19</f>
         <v>46314</v>
       </c>
-      <c r="I19" s="18" t="n">
-        <f aca="false">IF(G19=0,H19,H19+G19-1)</f>
+      <c r="I19" s="18">
+        <f t="shared" si="0"/>
         <v>46318</v>
       </c>
-      <c r="J19" s="15" t="n">
-        <f aca="false">INT((H19-Parámetros!$B$3)/7)+1</f>
+      <c r="J19" s="15">
+        <f>INT((H19-Parámetros!$B$3)/7)+1</f>
         <v>4</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="L19" s="19" t="n">
+      <c r="L19" s="19">
         <v>0</v>
       </c>
       <c r="M19" s="15" t="str">
-        <f aca="false">IF(L19&gt;=1,"Completada",IF($M$3&lt;H19,"Pendiente",IF($M$3&gt;I19,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
+        <f t="shared" si="1"/>
+        <v>En curso</v>
       </c>
       <c r="N19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=N$4,$H19&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=O$4,$H19&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=P$4,$H19&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=Q$4,$H19&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=R$4,$H19&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=S$4,$H19&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=T$4,$H19&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=U$4,$H19&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=V$4,$H19&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=W$4,$H19&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X19" s="20" t="str">
-        <f aca="false">IF(AND($G19=0,$H19&gt;=X$4,$H19&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="B20" s="15" t="n">
+      <c r="B20" s="15">
         <v>2</v>
       </c>
       <c r="C20" s="16" t="s">
@@ -2846,84 +2757,84 @@
       <c r="E20" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="17">
         <v>22</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="17">
         <v>9</v>
       </c>
-      <c r="H20" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F20</f>
+      <c r="H20" s="18">
+        <f>Parámetros!$B$3+F20</f>
         <v>46315</v>
       </c>
-      <c r="I20" s="18" t="n">
-        <f aca="false">IF(G20=0,H20,H20+G20-1)</f>
+      <c r="I20" s="18">
+        <f t="shared" si="0"/>
         <v>46323</v>
       </c>
-      <c r="J20" s="15" t="n">
-        <f aca="false">INT((H20-Parámetros!$B$3)/7)+1</f>
+      <c r="J20" s="15">
+        <f>INT((H20-Parámetros!$B$3)/7)+1</f>
         <v>4</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L20" s="19" t="n">
+      <c r="L20" s="19">
         <v>0</v>
       </c>
       <c r="M20" s="15" t="str">
-        <f aca="false">IF(L20&gt;=1,"Completada",IF($M$3&lt;H20,"Pendiente",IF($M$3&gt;I20,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=N$4,$H20&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=O$4,$H20&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=P$4,$H20&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=Q$4,$H20&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=R$4,$H20&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=S$4,$H20&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=T$4,$H20&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=U$4,$H20&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=V$4,$H20&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=W$4,$H20&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X20" s="20" t="str">
-        <f aca="false">IF(AND($G20=0,$H20&gt;=X$4,$H20&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="B21" s="15" t="n">
+      <c r="B21" s="15">
         <v>2</v>
       </c>
       <c r="C21" s="16" t="s">
@@ -2935,84 +2846,84 @@
       <c r="E21" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="17" t="n">
+      <c r="F21" s="17">
         <v>25</v>
       </c>
-      <c r="G21" s="17" t="n">
+      <c r="G21" s="17">
         <v>5</v>
       </c>
-      <c r="H21" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F21</f>
+      <c r="H21" s="18">
+        <f>Parámetros!$B$3+F21</f>
         <v>46318</v>
       </c>
-      <c r="I21" s="18" t="n">
-        <f aca="false">IF(G21=0,H21,H21+G21-1)</f>
+      <c r="I21" s="18">
+        <f t="shared" si="0"/>
         <v>46322</v>
       </c>
-      <c r="J21" s="15" t="n">
-        <f aca="false">INT((H21-Parámetros!$B$3)/7)+1</f>
+      <c r="J21" s="15">
+        <f>INT((H21-Parámetros!$B$3)/7)+1</f>
         <v>4</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L21" s="19" t="n">
+      <c r="L21" s="19">
         <v>0</v>
       </c>
       <c r="M21" s="15" t="str">
-        <f aca="false">IF(L21&gt;=1,"Completada",IF($M$3&lt;H21,"Pendiente",IF($M$3&gt;I21,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=N$4,$H21&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=O$4,$H21&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=P$4,$H21&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=Q$4,$H21&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=R$4,$H21&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=S$4,$H21&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=T$4,$H21&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=U$4,$H21&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=V$4,$H21&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=W$4,$H21&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X21" s="20" t="str">
-        <f aca="false">IF(AND($G21=0,$H21&gt;=X$4,$H21&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="15">
         <v>2</v>
       </c>
       <c r="C22" s="16" t="s">
@@ -3024,84 +2935,84 @@
       <c r="E22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F22" s="17" t="n">
+      <c r="F22" s="17">
         <v>28</v>
       </c>
-      <c r="G22" s="17" t="n">
+      <c r="G22" s="17">
         <v>5</v>
       </c>
-      <c r="H22" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F22</f>
+      <c r="H22" s="18">
+        <f>Parámetros!$B$3+F22</f>
         <v>46321</v>
       </c>
-      <c r="I22" s="18" t="n">
-        <f aca="false">IF(G22=0,H22,H22+G22-1)</f>
+      <c r="I22" s="18">
+        <f t="shared" si="0"/>
         <v>46325</v>
       </c>
-      <c r="J22" s="15" t="n">
-        <f aca="false">INT((H22-Parámetros!$B$3)/7)+1</f>
+      <c r="J22" s="15">
+        <f>INT((H22-Parámetros!$B$3)/7)+1</f>
         <v>5</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="L22" s="19" t="n">
+      <c r="L22" s="19">
         <v>0</v>
       </c>
       <c r="M22" s="15" t="str">
-        <f aca="false">IF(L22&gt;=1,"Completada",IF($M$3&lt;H22,"Pendiente",IF($M$3&gt;I22,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=N$4,$H22&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=O$4,$H22&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=P$4,$H22&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=Q$4,$H22&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=R$4,$H22&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=S$4,$H22&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=T$4,$H22&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=U$4,$H22&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=V$4,$H22&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=W$4,$H22&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X22" s="20" t="str">
-        <f aca="false">IF(AND($G22=0,$H22&gt;=X$4,$H22&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="15">
         <v>2</v>
       </c>
       <c r="C23" s="16" t="s">
@@ -3113,84 +3024,84 @@
       <c r="E23" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="17" t="n">
+      <c r="F23" s="17">
         <v>29</v>
       </c>
-      <c r="G23" s="17" t="n">
+      <c r="G23" s="17">
         <v>12</v>
       </c>
-      <c r="H23" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F23</f>
+      <c r="H23" s="18">
+        <f>Parámetros!$B$3+F23</f>
         <v>46322</v>
       </c>
-      <c r="I23" s="18" t="n">
-        <f aca="false">IF(G23=0,H23,H23+G23-1)</f>
+      <c r="I23" s="18">
+        <f t="shared" si="0"/>
         <v>46333</v>
       </c>
-      <c r="J23" s="15" t="n">
-        <f aca="false">INT((H23-Parámetros!$B$3)/7)+1</f>
+      <c r="J23" s="15">
+        <f>INT((H23-Parámetros!$B$3)/7)+1</f>
         <v>5</v>
       </c>
       <c r="K23" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="L23" s="19" t="n">
+      <c r="L23" s="19">
         <v>0</v>
       </c>
       <c r="M23" s="15" t="str">
-        <f aca="false">IF(L23&gt;=1,"Completada",IF($M$3&lt;H23,"Pendiente",IF($M$3&gt;I23,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=N$4,$H23&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=O$4,$H23&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=P$4,$H23&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=Q$4,$H23&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=R$4,$H23&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=S$4,$H23&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=T$4,$H23&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=U$4,$H23&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=V$4,$H23&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=W$4,$H23&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X23" s="20" t="str">
-        <f aca="false">IF(AND($G23=0,$H23&gt;=X$4,$H23&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="15">
         <v>2</v>
       </c>
       <c r="C24" s="16" t="s">
@@ -3202,84 +3113,84 @@
       <c r="E24" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F24" s="17" t="n">
+      <c r="F24" s="17">
         <v>41</v>
       </c>
-      <c r="G24" s="17" t="n">
+      <c r="G24" s="17">
         <v>9</v>
       </c>
-      <c r="H24" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F24</f>
+      <c r="H24" s="18">
+        <f>Parámetros!$B$3+F24</f>
         <v>46334</v>
       </c>
-      <c r="I24" s="18" t="n">
-        <f aca="false">IF(G24=0,H24,H24+G24-1)</f>
+      <c r="I24" s="18">
+        <f t="shared" si="0"/>
         <v>46342</v>
       </c>
-      <c r="J24" s="15" t="n">
-        <f aca="false">INT((H24-Parámetros!$B$3)/7)+1</f>
+      <c r="J24" s="15">
+        <f>INT((H24-Parámetros!$B$3)/7)+1</f>
         <v>6</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="L24" s="19" t="n">
+      <c r="L24" s="19">
         <v>0</v>
       </c>
       <c r="M24" s="15" t="str">
-        <f aca="false">IF(L24&gt;=1,"Completada",IF($M$3&lt;H24,"Pendiente",IF($M$3&gt;I24,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=N$4,$H24&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=O$4,$H24&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=P$4,$H24&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=Q$4,$H24&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=R$4,$H24&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=S$4,$H24&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=T$4,$H24&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=U$4,$H24&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=V$4,$H24&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=W$4,$H24&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X24" s="20" t="str">
-        <f aca="false">IF(AND($G24=0,$H24&gt;=X$4,$H24&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="B25" s="15" t="n">
+      <c r="B25" s="15">
         <v>2</v>
       </c>
       <c r="C25" s="16" t="s">
@@ -3291,84 +3202,84 @@
       <c r="E25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F25" s="17" t="n">
+      <c r="F25" s="17">
         <v>49</v>
       </c>
-      <c r="G25" s="17" t="n">
+      <c r="G25" s="17">
         <v>3</v>
       </c>
-      <c r="H25" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F25</f>
+      <c r="H25" s="18">
+        <f>Parámetros!$B$3+F25</f>
         <v>46342</v>
       </c>
-      <c r="I25" s="18" t="n">
-        <f aca="false">IF(G25=0,H25,H25+G25-1)</f>
+      <c r="I25" s="18">
+        <f t="shared" si="0"/>
         <v>46344</v>
       </c>
-      <c r="J25" s="15" t="n">
-        <f aca="false">INT((H25-Parámetros!$B$3)/7)+1</f>
+      <c r="J25" s="15">
+        <f>INT((H25-Parámetros!$B$3)/7)+1</f>
         <v>8</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="L25" s="19" t="n">
+      <c r="L25" s="19">
         <v>0</v>
       </c>
       <c r="M25" s="15" t="str">
-        <f aca="false">IF(L25&gt;=1,"Completada",IF($M$3&lt;H25,"Pendiente",IF($M$3&gt;I25,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=N$4,$H25&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="O25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=O$4,$H25&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="P25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=P$4,$H25&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="Q25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=Q$4,$H25&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="R25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=R$4,$H25&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="S25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=S$4,$H25&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="T25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=T$4,$H25&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="U25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=U$4,$H25&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="V25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=V$4,$H25&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="W25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=W$4,$H25&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="X25" s="20" t="str">
-        <f aca="false">IF(AND($G25=0,$H25&gt;=X$4,$H25&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="15">
         <v>2</v>
       </c>
       <c r="C26" s="22" t="s">
@@ -3380,85 +3291,85 @@
       <c r="E26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F26" s="15" t="n">
-        <f aca="false">H26-Parámetros!$B$3</f>
+      <c r="F26" s="15">
+        <f>H26-Parámetros!$B$3</f>
         <v>52</v>
       </c>
-      <c r="G26" s="15" t="n">
+      <c r="G26" s="15">
         <v>0</v>
       </c>
-      <c r="H26" s="23" t="n">
-        <f aca="false">Parámetros!$B$11</f>
+      <c r="H26" s="23">
+        <f>Parámetros!$B$11</f>
         <v>46345</v>
       </c>
-      <c r="I26" s="18" t="n">
-        <f aca="false">IF(G26=0,H26,H26+G26-1)</f>
+      <c r="I26" s="18">
+        <f t="shared" si="0"/>
         <v>46345</v>
       </c>
-      <c r="J26" s="15" t="n">
-        <f aca="false">INT((H26-Parámetros!$B$3)/7)+1</f>
+      <c r="J26" s="15">
+        <f>INT((H26-Parámetros!$B$3)/7)+1</f>
         <v>8</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="L26" s="19" t="n">
+      <c r="L26" s="19">
         <v>0</v>
       </c>
       <c r="M26" s="15" t="str">
-        <f aca="false">IF(L26&gt;=1,"Completada",IF($M$3&lt;H26,"Pendiente",IF($M$3&gt;I26,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=N$4,$H26&lt;=N$4+6),"◆","")</f>
+        <f t="shared" ref="N26:X36" si="4">IF(AND($G26=0,$H26&gt;=N$4,$H26&lt;=N$4+6),"◆","")</f>
         <v/>
       </c>
       <c r="O26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=O$4,$H26&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=P$4,$H26&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=Q$4,$H26&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=R$4,$H26&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=S$4,$H26&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=T$4,$H26&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=U$4,$H26&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v>◆</v>
       </c>
       <c r="V26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=V$4,$H26&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=W$4,$H26&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X26" s="20" t="str">
-        <f aca="false">IF(AND($G26=0,$H26&gt;=X$4,$H26&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="15">
         <v>3</v>
       </c>
       <c r="C27" s="16" t="s">
@@ -3470,84 +3381,84 @@
       <c r="E27" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="17" t="n">
+      <c r="F27" s="17">
         <v>36</v>
       </c>
-      <c r="G27" s="17" t="n">
+      <c r="G27" s="17">
         <v>12</v>
       </c>
-      <c r="H27" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F27</f>
+      <c r="H27" s="18">
+        <f>Parámetros!$B$3+F27</f>
         <v>46329</v>
       </c>
-      <c r="I27" s="18" t="n">
-        <f aca="false">IF(G27=0,H27,H27+G27-1)</f>
+      <c r="I27" s="18">
+        <f t="shared" si="0"/>
         <v>46340</v>
       </c>
-      <c r="J27" s="15" t="n">
-        <f aca="false">INT((H27-Parámetros!$B$3)/7)+1</f>
+      <c r="J27" s="15">
+        <f>INT((H27-Parámetros!$B$3)/7)+1</f>
         <v>6</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>86</v>
       </c>
-      <c r="L27" s="19" t="n">
+      <c r="L27" s="19">
         <v>0</v>
       </c>
       <c r="M27" s="15" t="str">
-        <f aca="false">IF(L27&gt;=1,"Completada",IF($M$3&lt;H27,"Pendiente",IF($M$3&gt;I27,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=N$4,$H27&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=O$4,$H27&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=P$4,$H27&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=Q$4,$H27&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=R$4,$H27&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=S$4,$H27&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=T$4,$H27&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=U$4,$H27&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=V$4,$H27&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=W$4,$H27&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X27" s="20" t="str">
-        <f aca="false">IF(AND($G27=0,$H27&gt;=X$4,$H27&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="15">
         <v>3</v>
       </c>
       <c r="C28" s="16" t="s">
@@ -3559,84 +3470,84 @@
       <c r="E28" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F28" s="17" t="n">
+      <c r="F28" s="17">
         <v>38</v>
       </c>
-      <c r="G28" s="17" t="n">
+      <c r="G28" s="17">
         <v>12</v>
       </c>
-      <c r="H28" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F28</f>
+      <c r="H28" s="18">
+        <f>Parámetros!$B$3+F28</f>
         <v>46331</v>
       </c>
-      <c r="I28" s="18" t="n">
-        <f aca="false">IF(G28=0,H28,H28+G28-1)</f>
+      <c r="I28" s="18">
+        <f t="shared" si="0"/>
         <v>46342</v>
       </c>
-      <c r="J28" s="15" t="n">
-        <f aca="false">INT((H28-Parámetros!$B$3)/7)+1</f>
+      <c r="J28" s="15">
+        <f>INT((H28-Parámetros!$B$3)/7)+1</f>
         <v>6</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="L28" s="19" t="n">
+      <c r="L28" s="19">
         <v>0</v>
       </c>
       <c r="M28" s="15" t="str">
-        <f aca="false">IF(L28&gt;=1,"Completada",IF($M$3&lt;H28,"Pendiente",IF($M$3&gt;I28,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=N$4,$H28&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=O$4,$H28&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=P$4,$H28&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=Q$4,$H28&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=R$4,$H28&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=S$4,$H28&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=T$4,$H28&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=U$4,$H28&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=V$4,$H28&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=W$4,$H28&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X28" s="20" t="str">
-        <f aca="false">IF(AND($G28=0,$H28&gt;=X$4,$H28&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="15">
         <v>3</v>
       </c>
       <c r="C29" s="16" t="s">
@@ -3648,84 +3559,84 @@
       <c r="E29" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F29" s="17" t="n">
+      <c r="F29" s="17">
         <v>45</v>
       </c>
-      <c r="G29" s="17" t="n">
+      <c r="G29" s="17">
         <v>8</v>
       </c>
-      <c r="H29" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F29</f>
+      <c r="H29" s="18">
+        <f>Parámetros!$B$3+F29</f>
         <v>46338</v>
       </c>
-      <c r="I29" s="18" t="n">
-        <f aca="false">IF(G29=0,H29,H29+G29-1)</f>
+      <c r="I29" s="18">
+        <f t="shared" si="0"/>
         <v>46345</v>
       </c>
-      <c r="J29" s="15" t="n">
-        <f aca="false">INT((H29-Parámetros!$B$3)/7)+1</f>
+      <c r="J29" s="15">
+        <f>INT((H29-Parámetros!$B$3)/7)+1</f>
         <v>7</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="L29" s="19" t="n">
+      <c r="L29" s="19">
         <v>0</v>
       </c>
       <c r="M29" s="15" t="str">
-        <f aca="false">IF(L29&gt;=1,"Completada",IF($M$3&lt;H29,"Pendiente",IF($M$3&gt;I29,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=N$4,$H29&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=O$4,$H29&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=P$4,$H29&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=Q$4,$H29&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=R$4,$H29&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=S$4,$H29&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=T$4,$H29&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=U$4,$H29&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=V$4,$H29&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=W$4,$H29&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X29" s="20" t="str">
-        <f aca="false">IF(AND($G29=0,$H29&gt;=X$4,$H29&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="15">
         <v>3</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -3737,84 +3648,84 @@
       <c r="E30" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F30" s="17" t="n">
+      <c r="F30" s="17">
         <v>52</v>
       </c>
-      <c r="G30" s="17" t="n">
+      <c r="G30" s="17">
         <v>5</v>
       </c>
-      <c r="H30" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F30</f>
+      <c r="H30" s="18">
+        <f>Parámetros!$B$3+F30</f>
         <v>46345</v>
       </c>
-      <c r="I30" s="18" t="n">
-        <f aca="false">IF(G30=0,H30,H30+G30-1)</f>
+      <c r="I30" s="18">
+        <f t="shared" si="0"/>
         <v>46349</v>
       </c>
-      <c r="J30" s="15" t="n">
-        <f aca="false">INT((H30-Parámetros!$B$3)/7)+1</f>
+      <c r="J30" s="15">
+        <f>INT((H30-Parámetros!$B$3)/7)+1</f>
         <v>8</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="L30" s="19" t="n">
+      <c r="L30" s="19">
         <v>0</v>
       </c>
       <c r="M30" s="15" t="str">
-        <f aca="false">IF(L30&gt;=1,"Completada",IF($M$3&lt;H30,"Pendiente",IF($M$3&gt;I30,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=N$4,$H30&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=O$4,$H30&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=P$4,$H30&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=Q$4,$H30&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=R$4,$H30&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=S$4,$H30&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=T$4,$H30&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=U$4,$H30&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=V$4,$H30&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=W$4,$H30&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X30" s="20" t="str">
-        <f aca="false">IF(AND($G30=0,$H30&gt;=X$4,$H30&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="B31" s="15" t="n">
+      <c r="B31" s="15">
         <v>3</v>
       </c>
       <c r="C31" s="16" t="s">
@@ -3826,84 +3737,84 @@
       <c r="E31" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F31" s="17" t="n">
+      <c r="F31" s="17">
         <v>54</v>
       </c>
-      <c r="G31" s="17" t="n">
+      <c r="G31" s="17">
         <v>5</v>
       </c>
-      <c r="H31" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F31</f>
+      <c r="H31" s="18">
+        <f>Parámetros!$B$3+F31</f>
         <v>46347</v>
       </c>
-      <c r="I31" s="18" t="n">
-        <f aca="false">IF(G31=0,H31,H31+G31-1)</f>
+      <c r="I31" s="18">
+        <f t="shared" si="0"/>
         <v>46351</v>
       </c>
-      <c r="J31" s="15" t="n">
-        <f aca="false">INT((H31-Parámetros!$B$3)/7)+1</f>
+      <c r="J31" s="15">
+        <f>INT((H31-Parámetros!$B$3)/7)+1</f>
         <v>8</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L31" s="19" t="n">
+      <c r="L31" s="19">
         <v>0</v>
       </c>
       <c r="M31" s="15" t="str">
-        <f aca="false">IF(L31&gt;=1,"Completada",IF($M$3&lt;H31,"Pendiente",IF($M$3&gt;I31,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=N$4,$H31&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=O$4,$H31&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=P$4,$H31&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=Q$4,$H31&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=R$4,$H31&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=S$4,$H31&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=T$4,$H31&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=U$4,$H31&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=V$4,$H31&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=W$4,$H31&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X31" s="20" t="str">
-        <f aca="false">IF(AND($G31=0,$H31&gt;=X$4,$H31&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B32" s="15" t="n">
+      <c r="B32" s="15">
         <v>3</v>
       </c>
       <c r="C32" s="16" t="s">
@@ -3915,84 +3826,84 @@
       <c r="E32" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F32" s="17" t="n">
+      <c r="F32" s="17">
         <v>45</v>
       </c>
-      <c r="G32" s="17" t="n">
+      <c r="G32" s="17">
         <v>10</v>
       </c>
-      <c r="H32" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F32</f>
+      <c r="H32" s="18">
+        <f>Parámetros!$B$3+F32</f>
         <v>46338</v>
       </c>
-      <c r="I32" s="18" t="n">
-        <f aca="false">IF(G32=0,H32,H32+G32-1)</f>
+      <c r="I32" s="18">
+        <f t="shared" si="0"/>
         <v>46347</v>
       </c>
-      <c r="J32" s="15" t="n">
-        <f aca="false">INT((H32-Parámetros!$B$3)/7)+1</f>
+      <c r="J32" s="15">
+        <f>INT((H32-Parámetros!$B$3)/7)+1</f>
         <v>7</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="L32" s="19" t="n">
+      <c r="L32" s="19">
         <v>0</v>
       </c>
       <c r="M32" s="15" t="str">
-        <f aca="false">IF(L32&gt;=1,"Completada",IF($M$3&lt;H32,"Pendiente",IF($M$3&gt;I32,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=N$4,$H32&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=O$4,$H32&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=P$4,$H32&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=Q$4,$H32&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=R$4,$H32&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=S$4,$H32&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=T$4,$H32&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=U$4,$H32&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=V$4,$H32&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=W$4,$H32&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X32" s="20" t="str">
-        <f aca="false">IF(AND($G32=0,$H32&gt;=X$4,$H32&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B33" s="15" t="n">
+      <c r="B33" s="15">
         <v>3</v>
       </c>
       <c r="C33" s="16" t="s">
@@ -4004,84 +3915,84 @@
       <c r="E33" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F33" s="17" t="n">
+      <c r="F33" s="17">
         <v>53</v>
       </c>
-      <c r="G33" s="17" t="n">
+      <c r="G33" s="17">
         <v>7</v>
       </c>
-      <c r="H33" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F33</f>
+      <c r="H33" s="18">
+        <f>Parámetros!$B$3+F33</f>
         <v>46346</v>
       </c>
-      <c r="I33" s="18" t="n">
-        <f aca="false">IF(G33=0,H33,H33+G33-1)</f>
+      <c r="I33" s="18">
+        <f t="shared" si="0"/>
         <v>46352</v>
       </c>
-      <c r="J33" s="15" t="n">
-        <f aca="false">INT((H33-Parámetros!$B$3)/7)+1</f>
+      <c r="J33" s="15">
+        <f>INT((H33-Parámetros!$B$3)/7)+1</f>
         <v>8</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>112</v>
       </c>
-      <c r="L33" s="19" t="n">
+      <c r="L33" s="19">
         <v>0</v>
       </c>
       <c r="M33" s="15" t="str">
-        <f aca="false">IF(L33&gt;=1,"Completada",IF($M$3&lt;H33,"Pendiente",IF($M$3&gt;I33,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=N$4,$H33&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=O$4,$H33&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=P$4,$H33&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=Q$4,$H33&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=R$4,$H33&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=S$4,$H33&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=T$4,$H33&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=U$4,$H33&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=V$4,$H33&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=W$4,$H33&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X33" s="20" t="str">
-        <f aca="false">IF(AND($G33=0,$H33&gt;=X$4,$H33&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="15" t="n">
+      <c r="B34" s="15">
         <v>3</v>
       </c>
       <c r="C34" s="16" t="s">
@@ -4093,84 +4004,84 @@
       <c r="E34" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F34" s="17" t="n">
+      <c r="F34" s="17">
         <v>58</v>
       </c>
-      <c r="G34" s="17" t="n">
+      <c r="G34" s="17">
         <v>4</v>
       </c>
-      <c r="H34" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F34</f>
+      <c r="H34" s="18">
+        <f>Parámetros!$B$3+F34</f>
         <v>46351</v>
       </c>
-      <c r="I34" s="18" t="n">
-        <f aca="false">IF(G34=0,H34,H34+G34-1)</f>
+      <c r="I34" s="18">
+        <f t="shared" si="0"/>
         <v>46354</v>
       </c>
-      <c r="J34" s="15" t="n">
-        <f aca="false">INT((H34-Parámetros!$B$3)/7)+1</f>
+      <c r="J34" s="15">
+        <f>INT((H34-Parámetros!$B$3)/7)+1</f>
         <v>9</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="L34" s="19" t="n">
+      <c r="L34" s="19">
         <v>0</v>
       </c>
       <c r="M34" s="15" t="str">
-        <f aca="false">IF(L34&gt;=1,"Completada",IF($M$3&lt;H34,"Pendiente",IF($M$3&gt;I34,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=N$4,$H34&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=O$4,$H34&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=P$4,$H34&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=Q$4,$H34&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=R$4,$H34&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=S$4,$H34&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=T$4,$H34&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=U$4,$H34&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=V$4,$H34&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=W$4,$H34&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X34" s="20" t="str">
-        <f aca="false">IF(AND($G34=0,$H34&gt;=X$4,$H34&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="B35" s="15" t="n">
+      <c r="B35" s="15">
         <v>3</v>
       </c>
       <c r="C35" s="16" t="s">
@@ -4182,84 +4093,84 @@
       <c r="E35" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F35" s="17" t="n">
+      <c r="F35" s="17">
         <v>61</v>
       </c>
-      <c r="G35" s="17" t="n">
+      <c r="G35" s="17">
         <v>3</v>
       </c>
-      <c r="H35" s="18" t="n">
-        <f aca="false">Parámetros!$B$3+F35</f>
+      <c r="H35" s="18">
+        <f>Parámetros!$B$3+F35</f>
         <v>46354</v>
       </c>
-      <c r="I35" s="18" t="n">
-        <f aca="false">IF(G35=0,H35,H35+G35-1)</f>
+      <c r="I35" s="18">
+        <f t="shared" si="0"/>
         <v>46356</v>
       </c>
-      <c r="J35" s="15" t="n">
-        <f aca="false">INT((H35-Parámetros!$B$3)/7)+1</f>
+      <c r="J35" s="15">
+        <f>INT((H35-Parámetros!$B$3)/7)+1</f>
         <v>9</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="L35" s="19" t="n">
+      <c r="L35" s="19">
         <v>0</v>
       </c>
       <c r="M35" s="15" t="str">
-        <f aca="false">IF(L35&gt;=1,"Completada",IF($M$3&lt;H35,"Pendiente",IF($M$3&gt;I35,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=N$4,$H35&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=O$4,$H35&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=P$4,$H35&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=Q$4,$H35&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=R$4,$H35&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=S$4,$H35&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=T$4,$H35&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=U$4,$H35&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=V$4,$H35&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=W$4,$H35&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="X35" s="20" t="str">
-        <f aca="false">IF(AND($G35=0,$H35&gt;=X$4,$H35&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B36" s="15">
         <v>3</v>
       </c>
       <c r="C36" s="22" t="s">
@@ -4271,104 +4182,104 @@
       <c r="E36" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F36" s="15" t="n">
-        <f aca="false">H36-Parámetros!$B$3</f>
+      <c r="F36" s="15">
+        <f>H36-Parámetros!$B$3</f>
         <v>64</v>
       </c>
-      <c r="G36" s="15" t="n">
+      <c r="G36" s="15">
         <v>0</v>
       </c>
-      <c r="H36" s="23" t="n">
-        <f aca="false">Parámetros!$B$12</f>
+      <c r="H36" s="23">
+        <f>Parámetros!$B$12</f>
         <v>46357</v>
       </c>
-      <c r="I36" s="18" t="n">
-        <f aca="false">IF(G36=0,H36,H36+G36-1)</f>
+      <c r="I36" s="18">
+        <f t="shared" si="0"/>
         <v>46357</v>
       </c>
-      <c r="J36" s="15" t="n">
-        <f aca="false">INT((H36-Parámetros!$B$3)/7)+1</f>
+      <c r="J36" s="15">
+        <f>INT((H36-Parámetros!$B$3)/7)+1</f>
         <v>10</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="L36" s="19" t="n">
+      <c r="L36" s="19">
         <v>0</v>
       </c>
       <c r="M36" s="15" t="str">
-        <f aca="false">IF(L36&gt;=1,"Completada",IF($M$3&lt;H36,"Pendiente",IF($M$3&gt;I36,"Atrasada","En curso")))</f>
+        <f t="shared" si="1"/>
         <v>Pendiente</v>
       </c>
       <c r="N36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=N$4,$H36&lt;=N$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="O36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=O$4,$H36&lt;=O$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="P36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=P$4,$H36&lt;=P$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="Q36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=Q$4,$H36&lt;=Q$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="R36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=R$4,$H36&lt;=R$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="S36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=S$4,$H36&lt;=S$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="T36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=T$4,$H36&lt;=T$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="U36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=U$4,$H36&lt;=U$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="V36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=V$4,$H36&lt;=V$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="W36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=W$4,$H36&lt;=W$4+6),"◆","")</f>
+        <f t="shared" si="4"/>
         <v>◆</v>
       </c>
       <c r="X36" s="20" t="str">
-        <f aca="false">IF(AND($G36=0,$H36&gt;=X$4,$H36&lt;=X$4+6),"◆","")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="C38" s="2" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B39" s="24"/>
       <c r="C39" s="6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B40" s="25"/>
       <c r="C40" s="6" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B41" s="26"/>
       <c r="C41" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B42" s="27" t="s">
         <v>137</v>
       </c>
@@ -4377,84 +4288,87 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N6:X36">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>AND($B6=1,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
+  <conditionalFormatting sqref="M6:M36">
+    <cfRule type="expression" dxfId="8" priority="7">
+      <formula>$M6="Completada"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>AND($B6=2,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
+    <cfRule type="expression" dxfId="7" priority="8">
+      <formula>$M6="En curso"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>AND($B6=3,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>$M6="Atrasada"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N4:X4">
+    <cfRule type="expression" dxfId="5" priority="6">
       <formula>AND($M$3&gt;=N$4,$M$3&lt;=N$4+6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N4:X4">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+  <conditionalFormatting sqref="N6:X36">
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>AND($B6=1,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>AND($B6=2,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="4">
+      <formula>AND($B6=3,$G6&gt;0,$H6&lt;=N$4+6,$I6&gt;=N$4)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>AND($M$3&gt;=N$4,$M$3&lt;=N$4+6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M6:M36">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>$M6="Completada"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>$M6="En curso"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>$M6="Atrasada"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation allowBlank="true" error="Elija un nombre de la lista de la hoja Parámetros." errorStyle="stop" errorTitle="Responsable" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E6:E36" type="list">
-      <formula1>Parámetros!$A$15:$A$20</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="false" error="Use un número entero de días (0 o más)." errorStyle="stop" errorTitle="Días" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F6:G15 F17:G25 F27:G35" type="whole">
+  <dataValidations count="2">
+    <dataValidation type="whole" operator="greaterThanOrEqual" errorTitle="Días" error="Use un número entero de días (0 o más)." sqref="F6:G15 F17:G25 F27:G35" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Use un porcentaje entre 0 % y 100 %." errorStyle="stop" errorTitle="% avance" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L36" type="decimal">
+    <dataValidation type="decimal" errorTitle="% avance" error="Use un porcentaje entre 0 % y 100 %." sqref="L6:L36" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" errorTitle="Responsable" error="Elija un nombre de la lista de la hoja Parámetros." xr:uid="{00000000-0002-0000-0100-000000000000}">
+          <x14:formula1>
+            <xm:f>Parámetros!$A$15:$A$20</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>E6:E36</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="5" width="12" customWidth="1"/>
+    <col min="6" max="7" width="11" customWidth="1"/>
+    <col min="8" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:12" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
@@ -4492,248 +4406,243 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="n">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
         <v>1</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="28">
         <v>0.2</v>
       </c>
-      <c r="D4" s="18" t="n">
-        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A4)</f>
+      <c r="D4" s="18">
+        <f>_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A4)</f>
         <v>46293</v>
       </c>
-      <c r="E4" s="18" t="n">
-        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A4)</f>
+      <c r="E4" s="18">
+        <f>_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A4)</f>
         <v>46314</v>
       </c>
-      <c r="F4" s="29" t="n">
-        <f aca="false">E4-D4+1</f>
+      <c r="F4" s="29">
+        <f>E4-D4+1</f>
         <v>22</v>
       </c>
-      <c r="G4" s="15" t="n">
-        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$36,A4,Cronograma!$G$6:$G$36,"&gt;0")</f>
+      <c r="G4" s="15">
+        <f>COUNTIFS(Cronograma!$B$6:$B$36,A4,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>10</v>
       </c>
-      <c r="H4" s="30" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A4)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A4),0)</f>
-        <v>0.790697674418605</v>
+      <c r="H4" s="30">
+        <f>IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A4)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A4),0)</f>
+        <v>1</v>
       </c>
       <c r="I4" s="15" t="str">
-        <f aca="false">IF(H4&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D4,"Pendiente",IF(Parámetros!$B$4&gt;E4,"Atrasada","En curso")))</f>
-        <v>En curso</v>
-      </c>
-      <c r="J4" s="23" t="n">
-        <f aca="false">Parámetros!$B$10</f>
+        <f>IF(H4&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D4,"Pendiente",IF(Parámetros!$B$4&gt;E4,"Atrasada","En curso")))</f>
+        <v>Completada</v>
+      </c>
+      <c r="J4" s="23">
+        <f>Parámetros!$B$10</f>
         <v>46314</v>
       </c>
-      <c r="K4" s="29" t="n">
-        <f aca="false">J4-Parámetros!$B$4</f>
-        <v>10</v>
-      </c>
-      <c r="L4" s="29" t="n">
-        <f aca="false">J4-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A4,Cronograma!$G$6:$G$36,"&gt;0")</f>
+      <c r="K4" s="29">
+        <f>J4-Parámetros!$B$4</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="29">
+        <f>J4-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A4,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="n">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
       <c r="B5" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="28">
         <v>0.1</v>
       </c>
-      <c r="D5" s="18" t="n">
-        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A5)</f>
+      <c r="D5" s="18">
+        <f>_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A5)</f>
         <v>46307</v>
       </c>
-      <c r="E5" s="18" t="n">
-        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A5)</f>
+      <c r="E5" s="18">
+        <f>_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A5)</f>
         <v>46345</v>
       </c>
-      <c r="F5" s="29" t="n">
-        <f aca="false">E5-D5+1</f>
+      <c r="F5" s="29">
+        <f>E5-D5+1</f>
         <v>39</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$36,A5,Cronograma!$G$6:$G$36,"&gt;0")</f>
+      <c r="G5" s="15">
+        <f>COUNTIFS(Cronograma!$B$6:$B$36,A5,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>9</v>
       </c>
-      <c r="H5" s="30" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A5)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A5),0)</f>
+      <c r="H5" s="30">
+        <f>IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A5)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A5),0)</f>
         <v>0</v>
       </c>
       <c r="I5" s="15" t="str">
-        <f aca="false">IF(H5&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D5,"Pendiente",IF(Parámetros!$B$4&gt;E5,"Atrasada","En curso")))</f>
-        <v>Pendiente</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <f aca="false">Parámetros!$B$11</f>
+        <f>IF(H5&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D5,"Pendiente",IF(Parámetros!$B$4&gt;E5,"Atrasada","En curso")))</f>
+        <v>En curso</v>
+      </c>
+      <c r="J5" s="23">
+        <f>Parámetros!$B$11</f>
         <v>46345</v>
       </c>
-      <c r="K5" s="29" t="n">
-        <f aca="false">J5-Parámetros!$B$4</f>
-        <v>41</v>
-      </c>
-      <c r="L5" s="29" t="n">
-        <f aca="false">J5-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A5,Cronograma!$G$6:$G$36,"&gt;0")</f>
+      <c r="K5" s="29">
+        <f>J5-Parámetros!$B$4</f>
+        <v>31</v>
+      </c>
+      <c r="L5" s="29">
+        <f>J5-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A5,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="n">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
       <c r="B6" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="28">
         <v>0.7</v>
       </c>
-      <c r="D6" s="18" t="n">
-        <f aca="false">_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A6)</f>
+      <c r="D6" s="18">
+        <f>_xlfn.MINIFS(Cronograma!$H$6:$H$36,Cronograma!$B$6:$B$36,A6)</f>
         <v>46329</v>
       </c>
-      <c r="E6" s="18" t="n">
-        <f aca="false">_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A6)</f>
+      <c r="E6" s="18">
+        <f>_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A6)</f>
         <v>46357</v>
       </c>
-      <c r="F6" s="29" t="n">
-        <f aca="false">E6-D6+1</f>
+      <c r="F6" s="29">
+        <f>E6-D6+1</f>
         <v>29</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <f aca="false">COUNTIFS(Cronograma!$B$6:$B$36,A6,Cronograma!$G$6:$G$36,"&gt;0")</f>
+      <c r="G6" s="15">
+        <f>COUNTIFS(Cronograma!$B$6:$B$36,A6,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>9</v>
       </c>
-      <c r="H6" s="30" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A6)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A6),0)</f>
+      <c r="H6" s="30">
+        <f>IFERROR(SUMPRODUCT((Cronograma!$B$6:$B$36=A6)*Cronograma!$G$6:$G$36*Cronograma!$L$6:$L$36)/SUMIFS(Cronograma!$G$6:$G$36,Cronograma!$B$6:$B$36,A6),0)</f>
         <v>0</v>
       </c>
       <c r="I6" s="15" t="str">
-        <f aca="false">IF(H6&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D6,"Pendiente",IF(Parámetros!$B$4&gt;E6,"Atrasada","En curso")))</f>
+        <f>IF(H6&gt;=1,"Completada",IF(Parámetros!$B$4&lt;D6,"Pendiente",IF(Parámetros!$B$4&gt;E6,"Atrasada","En curso")))</f>
         <v>Pendiente</v>
       </c>
-      <c r="J6" s="23" t="n">
-        <f aca="false">Parámetros!$B$12</f>
+      <c r="J6" s="23">
+        <f>Parámetros!$B$12</f>
         <v>46357</v>
       </c>
-      <c r="K6" s="29" t="n">
-        <f aca="false">J6-Parámetros!$B$4</f>
-        <v>53</v>
-      </c>
-      <c r="L6" s="29" t="n">
-        <f aca="false">J6-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A6,Cronograma!$G$6:$G$36,"&gt;0")</f>
+      <c r="K6" s="29">
+        <f>J6-Parámetros!$B$4</f>
+        <v>43</v>
+      </c>
+      <c r="L6" s="29">
+        <f>J6-_xlfn.MAXIFS(Cronograma!$I$6:$I$36,Cronograma!$B$6:$B$36,A6,Cronograma!$G$6:$G$36,"&gt;0")</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B7" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="C7" s="31" t="n">
-        <f aca="false">SUM(C4:C6)</f>
+      <c r="C7" s="31">
+        <f>SUM(C4:C6)</f>
         <v>1</v>
       </c>
-      <c r="D7" s="32" t="n">
-        <f aca="false">MIN(D4:D6)</f>
+      <c r="D7" s="32">
+        <f>MIN(D4:D6)</f>
         <v>46293</v>
       </c>
-      <c r="E7" s="32" t="n">
-        <f aca="false">MAX(E4:E6)</f>
+      <c r="E7" s="32">
+        <f>MAX(E4:E6)</f>
         <v>46357</v>
       </c>
-      <c r="F7" s="33" t="n">
-        <f aca="false">E7-D7+1</f>
+      <c r="F7" s="33">
+        <f>E7-D7+1</f>
         <v>65</v>
       </c>
-      <c r="G7" s="34" t="n">
-        <f aca="false">SUM(G4:G6)</f>
+      <c r="G7" s="34">
+        <f>SUM(G4:G6)</f>
         <v>28</v>
       </c>
-      <c r="H7" s="31" t="n">
-        <f aca="false">IFERROR(SUMPRODUCT(Cronograma!$G$6:$G$36,Cronograma!$L$6:$L$36)/SUM(Cronograma!$G$6:$G$36),0)</f>
-        <v>0.202380952380952</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="31">
+        <f>IFERROR(SUMPRODUCT(Cronograma!$G$6:$G$36,Cronograma!$L$6:$L$36)/SUM(Cronograma!$G$6:$G$36),0)</f>
+        <v>0.25595238095238093</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="35" t="n">
-        <f aca="false">SUMPRODUCT(C4:C6,H4:H6)</f>
-        <v>0.158139534883721</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="35">
+        <f>SUMPRODUCT(C4:C6,H4:H6)</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B11)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C11" s="6">
+        <f>COUNTIF(Cronograma!$M$6:$M$36,B11)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="6">
+        <f>COUNTIF(Cronograma!$M$6:$M$36,B12)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="C13" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B13)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="6">
+        <f>COUNTIF(Cronograma!$M$6:$M$36,B13)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="C14" s="6" t="n">
-        <f aca="false">COUNTIF(Cronograma!$M$6:$M$36,B14)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C14" s="6">
+        <f>COUNTIF(Cronograma!$M$6:$M$36,B14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="C16" s="2" t="n">
-        <f aca="false">SUM(C11:C14)</f>
+      <c r="C16" s="2">
+        <f>SUM(C11:C14)</f>
         <v>31</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="L4:L6">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>$L4&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>